--- a/config/sort_game_category_card_config.xlsx
+++ b/config/sort_game_category_card_config.xlsx
@@ -2581,7 +2581,7 @@
     <t>WORD_BREEDS_940</t>
   </si>
   <si>
-    <t>Breeds</t>
+    <t>Cats</t>
   </si>
   <si>
     <t>TID_SORT_GAME_CATEGORY_WORD_BREEDS</t>
@@ -8707,7 +8707,7 @@
       <c r="A214" s="4" t="s">
         <v>849</v>
       </c>
-      <c r="B214" s="4" t="s">
+      <c r="B214" s="5" t="s">
         <v>850</v>
       </c>
       <c r="C214" s="4" t="s">

--- a/config/sort_game_category_card_config.xlsx
+++ b/config/sort_game_category_card_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23960"/>
+    <workbookView windowWidth="29400" windowHeight="12880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2833,7 +2833,7 @@
     <t>TID_SORT_GAME_CATEGORY_PIC_GARMENTS</t>
   </si>
   <si>
-    <t>[GLOVES_PIC_GARMENTS_7,DRESS_PIC_GARMENTS_7,PANTS_PIC_GARMENTS_7,SHIRT_PIC_GARMENTS_7]</t>
+    <t>[GLOVES_PIC_GARMENTS_7,DRESS_PIC_GARMENTS_7,PANTS_PIC_GARMENTS_7,SHIRT_PIC_GARMENTS_7,COAT_PIC_GARMENTS_7]</t>
   </si>
   <si>
     <t>PIC_VEGGIE_8</t>
@@ -2857,7 +2857,7 @@
     <t>TID_SORT_GAME_CATEGORY_PIC_FRUITS</t>
   </si>
   <si>
-    <t>[ORANGE_PIC_FRUITS_9,KIWI_PIC_FRUITS_9,BANANA_PIC_FRUITS_9,APPLE_PIC_FRUITS_9]</t>
+    <t>[ORANGE_PIC_FRUITS_9,KIWI_PIC_FRUITS_9,BANANA_PIC_FRUITS_9,APPLE_PIC_FRUITS_9,POMEGRANATE_PIC_FRUITS_9,PEACH_PIC_FRUITS_9,PINEAPPLE_PIC_FRUITS_9,WATERMELON_PIC_FRUITS_9]</t>
   </si>
   <si>
     <t>PIC_CHAIR_10</t>
@@ -4335,6 +4335,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
@@ -4343,9 +4346,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4718,7 +4718,7 @@
       <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="3"/>
@@ -4761,14 +4761,14 @@
       <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="7">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" ht="107.75" spans="1:7">
       <c r="A7" s="4" t="s">
@@ -4780,14 +4780,14 @@
       <c r="C7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="7">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" ht="122.75" spans="1:7">
       <c r="A8" s="4" t="s">
@@ -4799,14 +4799,14 @@
       <c r="C8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="7">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
+      <c r="E8" s="8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" ht="183.75" spans="1:7">
       <c r="A9" s="4" t="s">
@@ -4818,14 +4818,14 @@
       <c r="C9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="7">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+      <c r="E9" s="8">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" ht="122.75" spans="1:7">
       <c r="A10" s="4" t="s">
@@ -4837,14 +4837,14 @@
       <c r="C10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="7">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" ht="76.75" spans="1:7">
       <c r="A11" s="4" t="s">
@@ -4856,14 +4856,14 @@
       <c r="C11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" ht="107.75" spans="1:7">
       <c r="A12" s="4" t="s">
@@ -4875,14 +4875,14 @@
       <c r="C12" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="7">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13" ht="122.75" spans="1:7">
       <c r="A13" s="4" t="s">
@@ -4894,14 +4894,14 @@
       <c r="C13" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="7">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" ht="122.75" spans="1:7">
       <c r="A14" s="4" t="s">
@@ -4913,14 +4913,14 @@
       <c r="C14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="7">
-        <v>1</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="E14" s="8">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" ht="137.75" spans="1:7">
       <c r="A15" s="4" t="s">
@@ -4932,14 +4932,14 @@
       <c r="C15" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="7">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
     </row>
     <row r="16" ht="92.75" spans="1:7">
       <c r="A16" s="4" t="s">
@@ -4951,14 +4951,14 @@
       <c r="C16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="7">
-        <v>1</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+      <c r="E16" s="8">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="17" ht="244.75" spans="1:7">
       <c r="A17" s="4" t="s">
@@ -4970,14 +4970,14 @@
       <c r="C17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="7">
-        <v>1</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="E17" s="8">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" ht="183.75" spans="1:7">
       <c r="A18" s="4" t="s">
@@ -4989,14 +4989,14 @@
       <c r="C18" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="7">
-        <v>1</v>
-      </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="E18" s="8">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" ht="198.75" spans="1:7">
       <c r="A19" s="4" t="s">
@@ -5008,14 +5008,14 @@
       <c r="C19" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="7">
-        <v>1</v>
-      </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="E19" s="8">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20" ht="137.75" spans="1:7">
       <c r="A20" s="4" t="s">
@@ -5027,14 +5027,14 @@
       <c r="C20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="7">
-        <v>1</v>
-      </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="E20" s="8">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21" ht="107.75" spans="1:7">
       <c r="A21" s="4" t="s">
@@ -5046,14 +5046,14 @@
       <c r="C21" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="7">
-        <v>1</v>
-      </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="E21" s="8">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
     </row>
     <row r="22" ht="92.75" spans="1:7">
       <c r="A22" s="4" t="s">
@@ -5065,14 +5065,14 @@
       <c r="C22" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="7">
-        <v>1</v>
-      </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="E22" s="8">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" ht="228.75" spans="1:7">
       <c r="A23" s="4" t="s">
@@ -5084,33 +5084,33 @@
       <c r="C23" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="7">
-        <v>1</v>
-      </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+      <c r="E23" s="8">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24" ht="213.75" spans="1:7">
       <c r="A24" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>90</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="7">
-        <v>1</v>
-      </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="E24" s="8">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
     </row>
     <row r="25" ht="198.75" spans="1:7">
       <c r="A25" s="4" t="s">
@@ -5122,14 +5122,14 @@
       <c r="C25" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E25" s="7">
-        <v>1</v>
-      </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="E25" s="8">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" ht="137.75" spans="1:7">
       <c r="A26" s="4" t="s">
@@ -5141,14 +5141,14 @@
       <c r="C26" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="7">
-        <v>1</v>
-      </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="E26" s="8">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
     </row>
     <row r="27" ht="122.75" spans="1:7">
       <c r="A27" s="4" t="s">
@@ -5160,14 +5160,14 @@
       <c r="C27" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E27" s="7">
-        <v>1</v>
-      </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="E27" s="8">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
     </row>
     <row r="28" ht="92.75" spans="1:7">
       <c r="A28" s="4" t="s">
@@ -5179,14 +5179,14 @@
       <c r="C28" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E28" s="7">
-        <v>1</v>
-      </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="E28" s="8">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
     </row>
     <row r="29" ht="228.75" spans="1:7">
       <c r="A29" s="4" t="s">
@@ -5198,14 +5198,14 @@
       <c r="C29" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E29" s="7">
-        <v>1</v>
-      </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="E29" s="8">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
     </row>
     <row r="30" ht="213.75" spans="1:7">
       <c r="A30" s="4" t="s">
@@ -5217,14 +5217,14 @@
       <c r="C30" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E30" s="7">
-        <v>1</v>
-      </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="E30" s="8">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" ht="122.75" spans="1:7">
       <c r="A31" s="4" t="s">
@@ -5236,14 +5236,14 @@
       <c r="C31" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E31" s="7">
-        <v>1</v>
-      </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="E31" s="8">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" ht="122.75" spans="1:7">
       <c r="A32" s="4" t="s">
@@ -5255,14 +5255,14 @@
       <c r="C32" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E32" s="7">
-        <v>1</v>
-      </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="E32" s="8">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
     </row>
     <row r="33" ht="107.75" spans="1:7">
       <c r="A33" s="4" t="s">
@@ -5274,14 +5274,14 @@
       <c r="C33" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="E33" s="7">
-        <v>1</v>
-      </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
+      <c r="E33" s="8">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
     </row>
     <row r="34" ht="92.75" spans="1:7">
       <c r="A34" s="4" t="s">
@@ -5293,14 +5293,14 @@
       <c r="C34" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="E34" s="7">
-        <v>1</v>
-      </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="E34" s="8">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
     </row>
     <row r="35" ht="92.75" spans="1:7">
       <c r="A35" s="4" t="s">
@@ -5312,14 +5312,14 @@
       <c r="C35" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E35" s="7">
-        <v>1</v>
-      </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
+      <c r="E35" s="8">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
     </row>
     <row r="36" ht="228.75" spans="1:7">
       <c r="A36" s="4" t="s">
@@ -5331,14 +5331,14 @@
       <c r="C36" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E36" s="7">
-        <v>1</v>
-      </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="E36" s="8">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
     </row>
     <row r="37" ht="168.75" spans="1:7">
       <c r="A37" s="4" t="s">
@@ -5350,14 +5350,14 @@
       <c r="C37" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E37" s="7">
-        <v>1</v>
-      </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+      <c r="E37" s="8">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
     </row>
     <row r="38" ht="183.75" spans="1:7">
       <c r="A38" s="4" t="s">
@@ -5369,14 +5369,14 @@
       <c r="C38" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E38" s="7">
-        <v>1</v>
-      </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="E38" s="8">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
     </row>
     <row r="39" ht="137.75" spans="1:7">
       <c r="A39" s="4" t="s">
@@ -5388,14 +5388,14 @@
       <c r="C39" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E39" s="7">
-        <v>1</v>
-      </c>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
+      <c r="E39" s="8">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
     </row>
     <row r="40" ht="274.75" spans="1:7">
       <c r="A40" s="4" t="s">
@@ -5407,14 +5407,14 @@
       <c r="C40" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E40" s="7">
-        <v>1</v>
-      </c>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
+      <c r="E40" s="8">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
     </row>
     <row r="41" ht="198.75" spans="1:7">
       <c r="A41" s="4" t="s">
@@ -5426,14 +5426,14 @@
       <c r="C41" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="E41" s="7">
-        <v>1</v>
-      </c>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
+      <c r="E41" s="8">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
     </row>
     <row r="42" ht="107.75" spans="1:7">
       <c r="A42" s="4" t="s">
@@ -5445,14 +5445,14 @@
       <c r="C42" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="E42" s="7">
-        <v>1</v>
-      </c>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
+      <c r="E42" s="8">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
     </row>
     <row r="43" ht="92.75" spans="1:7">
       <c r="A43" s="4" t="s">
@@ -5464,14 +5464,14 @@
       <c r="C43" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E43" s="7">
-        <v>1</v>
-      </c>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
+      <c r="E43" s="8">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
     </row>
     <row r="44" ht="92.75" spans="1:7">
       <c r="A44" s="4" t="s">
@@ -5483,14 +5483,14 @@
       <c r="C44" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E44" s="7">
-        <v>1</v>
-      </c>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
+      <c r="E44" s="8">
+        <v>1</v>
+      </c>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
     </row>
     <row r="45" ht="213.75" spans="1:7">
       <c r="A45" s="4" t="s">
@@ -5502,14 +5502,14 @@
       <c r="C45" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="E45" s="7">
-        <v>1</v>
-      </c>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
+      <c r="E45" s="8">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
     </row>
     <row r="46" ht="183.75" spans="1:7">
       <c r="A46" s="4" t="s">
@@ -5521,14 +5521,14 @@
       <c r="C46" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E46" s="7">
-        <v>1</v>
-      </c>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
+      <c r="E46" s="8">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
     </row>
     <row r="47" ht="122.75" spans="1:7">
       <c r="A47" s="4" t="s">
@@ -5540,14 +5540,14 @@
       <c r="C47" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E47" s="7">
-        <v>1</v>
-      </c>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
+      <c r="E47" s="8">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
     </row>
     <row r="48" ht="92.75" spans="1:7">
       <c r="A48" s="4" t="s">
@@ -5559,14 +5559,14 @@
       <c r="C48" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E48" s="7">
-        <v>1</v>
-      </c>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
+      <c r="E48" s="8">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
     </row>
     <row r="49" ht="76.75" spans="1:7">
       <c r="A49" s="4" t="s">
@@ -5578,14 +5578,14 @@
       <c r="C49" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="E49" s="7">
-        <v>1</v>
-      </c>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
+      <c r="E49" s="8">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
     </row>
     <row r="50" ht="244.75" spans="1:7">
       <c r="A50" s="4" t="s">
@@ -5597,14 +5597,14 @@
       <c r="C50" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="E50" s="7">
-        <v>1</v>
-      </c>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
+      <c r="E50" s="8">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
     </row>
     <row r="51" ht="244.75" spans="1:7">
       <c r="A51" s="4" t="s">
@@ -5616,14 +5616,14 @@
       <c r="C51" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="E51" s="7">
-        <v>1</v>
-      </c>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
+      <c r="E51" s="8">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
     </row>
     <row r="52" ht="213.75" spans="1:7">
       <c r="A52" s="4" t="s">
@@ -5635,14 +5635,14 @@
       <c r="C52" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E52" s="7">
-        <v>1</v>
-      </c>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
+      <c r="E52" s="8">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
     </row>
     <row r="53" ht="92.75" spans="1:7">
       <c r="A53" s="4" t="s">
@@ -5654,14 +5654,14 @@
       <c r="C53" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E53" s="7">
-        <v>1</v>
-      </c>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
+      <c r="E53" s="8">
+        <v>1</v>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
     </row>
     <row r="54" ht="107.75" spans="1:7">
       <c r="A54" s="4" t="s">
@@ -5673,14 +5673,14 @@
       <c r="C54" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E54" s="7">
-        <v>1</v>
-      </c>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
+      <c r="E54" s="8">
+        <v>1</v>
+      </c>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
     </row>
     <row r="55" ht="259.75" spans="1:7">
       <c r="A55" s="4" t="s">
@@ -5692,14 +5692,14 @@
       <c r="C55" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E55" s="7">
-        <v>1</v>
-      </c>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
+      <c r="E55" s="8">
+        <v>1</v>
+      </c>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
     </row>
     <row r="56" ht="92.75" spans="1:7">
       <c r="A56" s="4" t="s">
@@ -5711,14 +5711,14 @@
       <c r="C56" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="E56" s="7">
-        <v>1</v>
-      </c>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
+      <c r="E56" s="8">
+        <v>1</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
     </row>
     <row r="57" ht="289.75" spans="1:7">
       <c r="A57" s="4" t="s">
@@ -5730,14 +5730,14 @@
       <c r="C57" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="E57" s="7">
-        <v>1</v>
-      </c>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
+      <c r="E57" s="8">
+        <v>1</v>
+      </c>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
     </row>
     <row r="58" ht="259.75" spans="1:7">
       <c r="A58" s="4" t="s">
@@ -5749,14 +5749,14 @@
       <c r="C58" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="E58" s="7">
-        <v>1</v>
-      </c>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
+      <c r="E58" s="8">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
     </row>
     <row r="59" ht="198.75" spans="1:7">
       <c r="A59" s="4" t="s">
@@ -5768,14 +5768,14 @@
       <c r="C59" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="E59" s="7">
-        <v>1</v>
-      </c>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
+      <c r="E59" s="8">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
     </row>
     <row r="60" ht="137.75" spans="1:7">
       <c r="A60" s="4" t="s">
@@ -5787,14 +5787,14 @@
       <c r="C60" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E60" s="7">
-        <v>1</v>
-      </c>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
+      <c r="E60" s="8">
+        <v>1</v>
+      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
     </row>
     <row r="61" ht="137.75" spans="1:7">
       <c r="A61" s="4" t="s">
@@ -5806,14 +5806,14 @@
       <c r="C61" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="E61" s="7">
-        <v>1</v>
-      </c>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
+      <c r="E61" s="8">
+        <v>1</v>
+      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
     </row>
     <row r="62" ht="107.75" spans="1:7">
       <c r="A62" s="4" t="s">
@@ -5825,14 +5825,14 @@
       <c r="C62" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="E62" s="7">
-        <v>1</v>
-      </c>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
+      <c r="E62" s="8">
+        <v>1</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
     </row>
     <row r="63" ht="259.75" spans="1:7">
       <c r="A63" s="4" t="s">
@@ -5844,14 +5844,14 @@
       <c r="C63" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="E63" s="7">
-        <v>1</v>
-      </c>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
+      <c r="E63" s="8">
+        <v>1</v>
+      </c>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
     </row>
     <row r="64" ht="198.75" spans="1:7">
       <c r="A64" s="4" t="s">
@@ -5863,14 +5863,14 @@
       <c r="C64" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="E64" s="7">
-        <v>1</v>
-      </c>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
+      <c r="E64" s="8">
+        <v>1</v>
+      </c>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
     </row>
     <row r="65" ht="198.75" spans="1:7">
       <c r="A65" s="4" t="s">
@@ -5882,14 +5882,14 @@
       <c r="C65" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="E65" s="7">
-        <v>1</v>
-      </c>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
+      <c r="E65" s="8">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
     </row>
     <row r="66" ht="137.75" spans="1:7">
       <c r="A66" s="4" t="s">
@@ -5901,14 +5901,14 @@
       <c r="C66" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="E66" s="7">
-        <v>1</v>
-      </c>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
+      <c r="E66" s="8">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
     </row>
     <row r="67" ht="92.75" spans="1:7">
       <c r="A67" s="4" t="s">
@@ -5920,14 +5920,14 @@
       <c r="C67" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="E67" s="7">
-        <v>1</v>
-      </c>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
+      <c r="E67" s="8">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
     </row>
     <row r="68" ht="92.75" spans="1:7">
       <c r="A68" s="4" t="s">
@@ -5939,14 +5939,14 @@
       <c r="C68" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="E68" s="7">
-        <v>1</v>
-      </c>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
+      <c r="E68" s="8">
+        <v>1</v>
+      </c>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
     </row>
     <row r="69" ht="137.75" spans="1:7">
       <c r="A69" s="4" t="s">
@@ -5958,14 +5958,14 @@
       <c r="C69" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="E69" s="7">
-        <v>1</v>
-      </c>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
+      <c r="E69" s="8">
+        <v>1</v>
+      </c>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
     </row>
     <row r="70" ht="107.75" spans="1:7">
       <c r="A70" s="4" t="s">
@@ -5977,14 +5977,14 @@
       <c r="C70" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="E70" s="7">
-        <v>1</v>
-      </c>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
+      <c r="E70" s="8">
+        <v>1</v>
+      </c>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
     </row>
     <row r="71" ht="107.75" spans="1:7">
       <c r="A71" s="4" t="s">
@@ -5996,14 +5996,14 @@
       <c r="C71" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="E71" s="7">
-        <v>1</v>
-      </c>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
+      <c r="E71" s="8">
+        <v>1</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
     </row>
     <row r="72" ht="244.75" spans="1:7">
       <c r="A72" s="4" t="s">
@@ -6015,14 +6015,14 @@
       <c r="C72" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="E72" s="7">
-        <v>1</v>
-      </c>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
+      <c r="E72" s="8">
+        <v>1</v>
+      </c>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
     </row>
     <row r="73" ht="213.75" spans="1:7">
       <c r="A73" s="4" t="s">
@@ -6034,14 +6034,14 @@
       <c r="C73" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="E73" s="7">
-        <v>1</v>
-      </c>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
+      <c r="E73" s="8">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
     </row>
     <row r="74" ht="137.75" spans="1:7">
       <c r="A74" s="4" t="s">
@@ -6053,14 +6053,14 @@
       <c r="C74" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="E74" s="7">
-        <v>1</v>
-      </c>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
+      <c r="E74" s="8">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
     </row>
     <row r="75" ht="107.75" spans="1:7">
       <c r="A75" s="4" t="s">
@@ -6072,14 +6072,14 @@
       <c r="C75" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="E75" s="7">
-        <v>1</v>
-      </c>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
+      <c r="E75" s="8">
+        <v>1</v>
+      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
     </row>
     <row r="76" ht="107.75" spans="1:7">
       <c r="A76" s="4" t="s">
@@ -6091,14 +6091,14 @@
       <c r="C76" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="E76" s="7">
-        <v>1</v>
-      </c>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
+      <c r="E76" s="8">
+        <v>1</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
     </row>
     <row r="77" ht="289.75" spans="1:7">
       <c r="A77" s="4" t="s">
@@ -6110,14 +6110,14 @@
       <c r="C77" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="E77" s="7">
-        <v>1</v>
-      </c>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
+      <c r="E77" s="8">
+        <v>1</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
     </row>
     <row r="78" ht="244.75" spans="1:7">
       <c r="A78" s="4" t="s">
@@ -6129,14 +6129,14 @@
       <c r="C78" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="E78" s="7">
-        <v>1</v>
-      </c>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
+      <c r="E78" s="8">
+        <v>1</v>
+      </c>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
     </row>
     <row r="79" ht="122.75" spans="1:7">
       <c r="A79" s="4" t="s">
@@ -6148,33 +6148,33 @@
       <c r="C79" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="E79" s="7">
-        <v>1</v>
-      </c>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
+      <c r="E79" s="8">
+        <v>1</v>
+      </c>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
     </row>
     <row r="80" ht="137.75" spans="1:7">
       <c r="A80" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="6" t="s">
         <v>314</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D80" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="E80" s="7">
-        <v>1</v>
-      </c>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
+      <c r="E80" s="8">
+        <v>1</v>
+      </c>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
     </row>
     <row r="81" ht="92.75" spans="1:7">
       <c r="A81" s="4" t="s">
@@ -6186,14 +6186,14 @@
       <c r="C81" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="E81" s="7">
-        <v>1</v>
-      </c>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
+      <c r="E81" s="8">
+        <v>1</v>
+      </c>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
     </row>
     <row r="82" ht="244.75" spans="1:7">
       <c r="A82" s="4" t="s">
@@ -6205,14 +6205,14 @@
       <c r="C82" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="E82" s="7">
-        <v>1</v>
-      </c>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
+      <c r="E82" s="8">
+        <v>1</v>
+      </c>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
     </row>
     <row r="83" ht="137.75" spans="1:7">
       <c r="A83" s="4" t="s">
@@ -6224,14 +6224,14 @@
       <c r="C83" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="E83" s="7">
-        <v>1</v>
-      </c>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
+      <c r="E83" s="8">
+        <v>1</v>
+      </c>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
     </row>
     <row r="84" ht="122.75" spans="1:7">
       <c r="A84" s="4" t="s">
@@ -6243,14 +6243,14 @@
       <c r="C84" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="E84" s="7">
-        <v>1</v>
-      </c>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
+      <c r="E84" s="8">
+        <v>1</v>
+      </c>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
     </row>
     <row r="85" ht="152.75" spans="1:7">
       <c r="A85" s="4" t="s">
@@ -6262,14 +6262,14 @@
       <c r="C85" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="E85" s="7">
-        <v>1</v>
-      </c>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
+      <c r="E85" s="8">
+        <v>1</v>
+      </c>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
     </row>
     <row r="86" ht="107.75" spans="1:7">
       <c r="A86" s="4" t="s">
@@ -6281,14 +6281,14 @@
       <c r="C86" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="E86" s="7">
-        <v>1</v>
-      </c>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
+      <c r="E86" s="8">
+        <v>1</v>
+      </c>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
     </row>
     <row r="87" ht="92.75" spans="1:7">
       <c r="A87" s="4" t="s">
@@ -6300,14 +6300,14 @@
       <c r="C87" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="E87" s="7">
-        <v>1</v>
-      </c>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8"/>
+      <c r="E87" s="8">
+        <v>1</v>
+      </c>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
     </row>
     <row r="88" ht="274.75" spans="1:7">
       <c r="A88" s="4" t="s">
@@ -6319,14 +6319,14 @@
       <c r="C88" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E88" s="7">
-        <v>1</v>
-      </c>
-      <c r="F88" s="8"/>
-      <c r="G88" s="8"/>
+      <c r="E88" s="8">
+        <v>1</v>
+      </c>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
     </row>
     <row r="89" ht="198.75" spans="1:7">
       <c r="A89" s="4" t="s">
@@ -6338,14 +6338,14 @@
       <c r="C89" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D89" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="E89" s="7">
-        <v>1</v>
-      </c>
-      <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
+      <c r="E89" s="8">
+        <v>1</v>
+      </c>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
     </row>
     <row r="90" ht="198.75" spans="1:7">
       <c r="A90" s="4" t="s">
@@ -6357,14 +6357,14 @@
       <c r="C90" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D90" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="E90" s="7">
-        <v>1</v>
-      </c>
-      <c r="F90" s="8"/>
-      <c r="G90" s="8"/>
+      <c r="E90" s="8">
+        <v>1</v>
+      </c>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
     </row>
     <row r="91" ht="92.75" spans="1:7">
       <c r="A91" s="4" t="s">
@@ -6376,14 +6376,14 @@
       <c r="C91" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="E91" s="7">
-        <v>1</v>
-      </c>
-      <c r="F91" s="8"/>
-      <c r="G91" s="8"/>
+      <c r="E91" s="8">
+        <v>1</v>
+      </c>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
     </row>
     <row r="92" ht="107.75" spans="1:7">
       <c r="A92" s="4" t="s">
@@ -6395,14 +6395,14 @@
       <c r="C92" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="E92" s="7">
-        <v>1</v>
-      </c>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
+      <c r="E92" s="8">
+        <v>1</v>
+      </c>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
     </row>
     <row r="93" ht="198.75" spans="1:7">
       <c r="A93" s="4" t="s">
@@ -6414,14 +6414,14 @@
       <c r="C93" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D93" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="E93" s="7">
-        <v>1</v>
-      </c>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
+      <c r="E93" s="8">
+        <v>1</v>
+      </c>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
     </row>
     <row r="94" ht="228.75" spans="1:7">
       <c r="A94" s="4" t="s">
@@ -6433,14 +6433,14 @@
       <c r="C94" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="D94" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="E94" s="7">
-        <v>1</v>
-      </c>
-      <c r="F94" s="8"/>
-      <c r="G94" s="8"/>
+      <c r="E94" s="8">
+        <v>1</v>
+      </c>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
     </row>
     <row r="95" ht="152.75" spans="1:7">
       <c r="A95" s="4" t="s">
@@ -6452,14 +6452,14 @@
       <c r="C95" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="D95" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="E95" s="7">
-        <v>1</v>
-      </c>
-      <c r="F95" s="8"/>
-      <c r="G95" s="8"/>
+      <c r="E95" s="8">
+        <v>1</v>
+      </c>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
     </row>
     <row r="96" ht="107.75" spans="1:7">
       <c r="A96" s="4" t="s">
@@ -6471,14 +6471,14 @@
       <c r="C96" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="D96" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="E96" s="7">
-        <v>1</v>
-      </c>
-      <c r="F96" s="8"/>
-      <c r="G96" s="8"/>
+      <c r="E96" s="8">
+        <v>1</v>
+      </c>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
     </row>
     <row r="97" ht="92.75" spans="1:7">
       <c r="A97" s="4" t="s">
@@ -6490,14 +6490,14 @@
       <c r="C97" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="D97" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="E97" s="7">
-        <v>1</v>
-      </c>
-      <c r="F97" s="8"/>
-      <c r="G97" s="8"/>
+      <c r="E97" s="8">
+        <v>1</v>
+      </c>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
     </row>
     <row r="98" ht="274.75" spans="1:7">
       <c r="A98" s="4" t="s">
@@ -6509,33 +6509,33 @@
       <c r="C98" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D98" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="E98" s="7">
-        <v>1</v>
-      </c>
-      <c r="F98" s="8"/>
-      <c r="G98" s="8"/>
+      <c r="E98" s="8">
+        <v>1</v>
+      </c>
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
     </row>
     <row r="99" ht="213.75" spans="1:7">
       <c r="A99" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="6" t="s">
         <v>390</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="E99" s="7">
-        <v>1</v>
-      </c>
-      <c r="F99" s="8"/>
-      <c r="G99" s="8"/>
+      <c r="E99" s="8">
+        <v>1</v>
+      </c>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
     </row>
     <row r="100" ht="168.75" spans="1:7">
       <c r="A100" s="4" t="s">
@@ -6547,14 +6547,14 @@
       <c r="C100" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D100" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="E100" s="7">
-        <v>1</v>
-      </c>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
+      <c r="E100" s="8">
+        <v>1</v>
+      </c>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
     </row>
     <row r="101" ht="137.75" spans="1:7">
       <c r="A101" s="4" t="s">
@@ -6566,14 +6566,14 @@
       <c r="C101" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="D101" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="E101" s="7">
-        <v>1</v>
-      </c>
-      <c r="F101" s="8"/>
-      <c r="G101" s="8"/>
+      <c r="E101" s="8">
+        <v>1</v>
+      </c>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
     </row>
     <row r="102" ht="107.75" spans="1:7">
       <c r="A102" s="4" t="s">
@@ -6585,14 +6585,14 @@
       <c r="C102" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="D102" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="E102" s="7">
-        <v>1</v>
-      </c>
-      <c r="F102" s="8"/>
-      <c r="G102" s="8"/>
+      <c r="E102" s="8">
+        <v>1</v>
+      </c>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
     </row>
     <row r="103" ht="259.75" spans="1:7">
       <c r="A103" s="4" t="s">
@@ -6604,14 +6604,14 @@
       <c r="C103" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="D103" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="E103" s="7">
-        <v>1</v>
-      </c>
-      <c r="F103" s="8"/>
-      <c r="G103" s="8"/>
+      <c r="E103" s="8">
+        <v>1</v>
+      </c>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
     </row>
     <row r="104" ht="107.75" spans="1:7">
       <c r="A104" s="4" t="s">
@@ -6623,14 +6623,14 @@
       <c r="C104" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="D104" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="E104" s="7">
-        <v>1</v>
-      </c>
-      <c r="F104" s="8"/>
-      <c r="G104" s="8"/>
+      <c r="E104" s="8">
+        <v>1</v>
+      </c>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
     </row>
     <row r="105" ht="137.75" spans="1:7">
       <c r="A105" s="4" t="s">
@@ -6642,14 +6642,14 @@
       <c r="C105" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="D105" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="E105" s="7">
-        <v>1</v>
-      </c>
-      <c r="F105" s="8"/>
-      <c r="G105" s="8"/>
+      <c r="E105" s="8">
+        <v>1</v>
+      </c>
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
     </row>
     <row r="106" ht="122.75" spans="1:7">
       <c r="A106" s="4" t="s">
@@ -6661,14 +6661,14 @@
       <c r="C106" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="D106" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="E106" s="7">
-        <v>1</v>
-      </c>
-      <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
+      <c r="E106" s="8">
+        <v>1</v>
+      </c>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
     </row>
     <row r="107" ht="122.75" spans="1:7">
       <c r="A107" s="4" t="s">
@@ -6680,14 +6680,14 @@
       <c r="C107" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="D107" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="E107" s="7">
-        <v>1</v>
-      </c>
-      <c r="F107" s="8"/>
-      <c r="G107" s="8"/>
+      <c r="E107" s="8">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
     </row>
     <row r="108" ht="198.75" spans="1:7">
       <c r="A108" s="4" t="s">
@@ -6699,14 +6699,14 @@
       <c r="C108" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D108" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="E108" s="7">
-        <v>1</v>
-      </c>
-      <c r="F108" s="8"/>
-      <c r="G108" s="8"/>
+      <c r="E108" s="8">
+        <v>1</v>
+      </c>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
     </row>
     <row r="109" ht="137.75" spans="1:7">
       <c r="A109" s="4" t="s">
@@ -6718,14 +6718,14 @@
       <c r="C109" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="D109" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E109" s="7">
-        <v>1</v>
-      </c>
-      <c r="F109" s="8"/>
-      <c r="G109" s="8"/>
+      <c r="E109" s="8">
+        <v>1</v>
+      </c>
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
     </row>
     <row r="110" ht="107.75" spans="1:7">
       <c r="A110" s="4" t="s">
@@ -6737,33 +6737,33 @@
       <c r="C110" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="D110" s="4" t="s">
+      <c r="D110" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="E110" s="7">
-        <v>1</v>
-      </c>
-      <c r="F110" s="8"/>
-      <c r="G110" s="8"/>
+      <c r="E110" s="8">
+        <v>1</v>
+      </c>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
     </row>
     <row r="111" ht="228.75" spans="1:7">
       <c r="A111" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="B111" s="5" t="s">
+      <c r="B111" s="6" t="s">
         <v>438</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D111" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="E111" s="7">
-        <v>1</v>
-      </c>
-      <c r="F111" s="8"/>
-      <c r="G111" s="8"/>
+      <c r="E111" s="8">
+        <v>1</v>
+      </c>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
     </row>
     <row r="112" ht="137.75" spans="1:7">
       <c r="A112" s="4" t="s">
@@ -6775,14 +6775,14 @@
       <c r="C112" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="D112" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="E112" s="7">
-        <v>1</v>
-      </c>
-      <c r="F112" s="8"/>
-      <c r="G112" s="8"/>
+      <c r="E112" s="8">
+        <v>1</v>
+      </c>
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
     </row>
     <row r="113" ht="137.75" spans="1:7">
       <c r="A113" s="4" t="s">
@@ -6794,14 +6794,14 @@
       <c r="C113" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="D113" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="E113" s="7">
-        <v>1</v>
-      </c>
-      <c r="F113" s="8"/>
-      <c r="G113" s="8"/>
+      <c r="E113" s="8">
+        <v>1</v>
+      </c>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
     </row>
     <row r="114" ht="137.75" spans="1:7">
       <c r="A114" s="4" t="s">
@@ -6813,14 +6813,14 @@
       <c r="C114" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="D114" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="E114" s="7">
-        <v>1</v>
-      </c>
-      <c r="F114" s="8"/>
-      <c r="G114" s="8"/>
+      <c r="E114" s="8">
+        <v>1</v>
+      </c>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
     </row>
     <row r="115" ht="122.75" spans="1:7">
       <c r="A115" s="4" t="s">
@@ -6832,14 +6832,14 @@
       <c r="C115" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="D115" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="E115" s="7">
-        <v>1</v>
-      </c>
-      <c r="F115" s="8"/>
-      <c r="G115" s="8"/>
+      <c r="E115" s="8">
+        <v>1</v>
+      </c>
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
     </row>
     <row r="116" ht="107.75" spans="1:7">
       <c r="A116" s="4" t="s">
@@ -6851,14 +6851,14 @@
       <c r="C116" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D116" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="E116" s="7">
-        <v>1</v>
-      </c>
-      <c r="F116" s="8"/>
-      <c r="G116" s="8"/>
+      <c r="E116" s="8">
+        <v>1</v>
+      </c>
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
     </row>
     <row r="117" ht="274.75" spans="1:7">
       <c r="A117" s="4" t="s">
@@ -6870,14 +6870,14 @@
       <c r="C117" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="D117" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="E117" s="7">
-        <v>1</v>
-      </c>
-      <c r="F117" s="8"/>
-      <c r="G117" s="8"/>
+      <c r="E117" s="8">
+        <v>1</v>
+      </c>
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
     </row>
     <row r="118" ht="183.75" spans="1:7">
       <c r="A118" s="4" t="s">
@@ -6889,14 +6889,14 @@
       <c r="C118" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="D118" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="E118" s="7">
-        <v>1</v>
-      </c>
-      <c r="F118" s="8"/>
-      <c r="G118" s="8"/>
+      <c r="E118" s="8">
+        <v>1</v>
+      </c>
+      <c r="F118" s="4"/>
+      <c r="G118" s="4"/>
     </row>
     <row r="119" ht="152.75" spans="1:7">
       <c r="A119" s="4" t="s">
@@ -6908,14 +6908,14 @@
       <c r="C119" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="D119" s="4" t="s">
+      <c r="D119" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="E119" s="7">
-        <v>1</v>
-      </c>
-      <c r="F119" s="8"/>
-      <c r="G119" s="8"/>
+      <c r="E119" s="8">
+        <v>1</v>
+      </c>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
     </row>
     <row r="120" ht="137.75" spans="1:7">
       <c r="A120" s="4" t="s">
@@ -6927,14 +6927,14 @@
       <c r="C120" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="D120" s="4" t="s">
+      <c r="D120" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E120" s="7">
-        <v>1</v>
-      </c>
-      <c r="F120" s="8"/>
-      <c r="G120" s="8"/>
+      <c r="E120" s="8">
+        <v>1</v>
+      </c>
+      <c r="F120" s="4"/>
+      <c r="G120" s="4"/>
     </row>
     <row r="121" ht="107.75" spans="1:7">
       <c r="A121" s="4" t="s">
@@ -6946,14 +6946,14 @@
       <c r="C121" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="D121" s="4" t="s">
+      <c r="D121" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="E121" s="7">
-        <v>1</v>
-      </c>
-      <c r="F121" s="8"/>
-      <c r="G121" s="8"/>
+      <c r="E121" s="8">
+        <v>1</v>
+      </c>
+      <c r="F121" s="4"/>
+      <c r="G121" s="4"/>
     </row>
     <row r="122" ht="92.75" spans="1:7">
       <c r="A122" s="4" t="s">
@@ -6965,14 +6965,14 @@
       <c r="C122" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="D122" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="E122" s="7">
-        <v>1</v>
-      </c>
-      <c r="F122" s="8"/>
-      <c r="G122" s="8"/>
+      <c r="E122" s="8">
+        <v>1</v>
+      </c>
+      <c r="F122" s="4"/>
+      <c r="G122" s="4"/>
     </row>
     <row r="123" ht="137.75" spans="1:7">
       <c r="A123" s="4" t="s">
@@ -6984,14 +6984,14 @@
       <c r="C123" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="D123" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="E123" s="7">
-        <v>1</v>
-      </c>
-      <c r="F123" s="8"/>
-      <c r="G123" s="8"/>
+      <c r="E123" s="8">
+        <v>1</v>
+      </c>
+      <c r="F123" s="4"/>
+      <c r="G123" s="4"/>
     </row>
     <row r="124" ht="92.75" spans="1:7">
       <c r="A124" s="4" t="s">
@@ -7003,14 +7003,14 @@
       <c r="C124" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="D124" s="4" t="s">
+      <c r="D124" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="E124" s="7">
-        <v>1</v>
-      </c>
-      <c r="F124" s="8"/>
-      <c r="G124" s="8"/>
+      <c r="E124" s="8">
+        <v>1</v>
+      </c>
+      <c r="F124" s="4"/>
+      <c r="G124" s="4"/>
     </row>
     <row r="125" ht="274.75" spans="1:7">
       <c r="A125" s="4" t="s">
@@ -7022,14 +7022,14 @@
       <c r="C125" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="D125" s="4" t="s">
+      <c r="D125" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="E125" s="7">
-        <v>1</v>
-      </c>
-      <c r="F125" s="8"/>
-      <c r="G125" s="8"/>
+      <c r="E125" s="8">
+        <v>1</v>
+      </c>
+      <c r="F125" s="4"/>
+      <c r="G125" s="4"/>
     </row>
     <row r="126" ht="137.75" spans="1:7">
       <c r="A126" s="4" t="s">
@@ -7041,14 +7041,14 @@
       <c r="C126" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="D126" s="4" t="s">
+      <c r="D126" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="E126" s="7">
-        <v>1</v>
-      </c>
-      <c r="F126" s="8"/>
-      <c r="G126" s="8"/>
+      <c r="E126" s="8">
+        <v>1</v>
+      </c>
+      <c r="F126" s="4"/>
+      <c r="G126" s="4"/>
     </row>
     <row r="127" ht="152.75" spans="1:7">
       <c r="A127" s="4" t="s">
@@ -7060,14 +7060,14 @@
       <c r="C127" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="D127" s="4" t="s">
+      <c r="D127" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="E127" s="7">
-        <v>1</v>
-      </c>
-      <c r="F127" s="8"/>
-      <c r="G127" s="8"/>
+      <c r="E127" s="8">
+        <v>1</v>
+      </c>
+      <c r="F127" s="4"/>
+      <c r="G127" s="4"/>
     </row>
     <row r="128" ht="76.75" spans="1:7">
       <c r="A128" s="4" t="s">
@@ -7079,14 +7079,14 @@
       <c r="C128" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="D128" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="E128" s="7">
-        <v>1</v>
-      </c>
-      <c r="F128" s="8"/>
-      <c r="G128" s="8"/>
+      <c r="E128" s="8">
+        <v>1</v>
+      </c>
+      <c r="F128" s="4"/>
+      <c r="G128" s="4"/>
     </row>
     <row r="129" ht="107.75" spans="1:7">
       <c r="A129" s="4" t="s">
@@ -7098,14 +7098,14 @@
       <c r="C129" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="D129" s="4" t="s">
+      <c r="D129" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="E129" s="7">
-        <v>1</v>
-      </c>
-      <c r="F129" s="8"/>
-      <c r="G129" s="8"/>
+      <c r="E129" s="8">
+        <v>1</v>
+      </c>
+      <c r="F129" s="4"/>
+      <c r="G129" s="4"/>
     </row>
     <row r="130" ht="259.75" spans="1:7">
       <c r="A130" s="4" t="s">
@@ -7117,14 +7117,14 @@
       <c r="C130" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="D130" s="4" t="s">
+      <c r="D130" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="E130" s="7">
-        <v>1</v>
-      </c>
-      <c r="F130" s="8"/>
-      <c r="G130" s="8"/>
+      <c r="E130" s="8">
+        <v>1</v>
+      </c>
+      <c r="F130" s="4"/>
+      <c r="G130" s="4"/>
     </row>
     <row r="131" ht="107.75" spans="1:7">
       <c r="A131" s="4" t="s">
@@ -7136,14 +7136,14 @@
       <c r="C131" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="D131" s="4" t="s">
+      <c r="D131" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="E131" s="7">
-        <v>1</v>
-      </c>
-      <c r="F131" s="8"/>
-      <c r="G131" s="8"/>
+      <c r="E131" s="8">
+        <v>1</v>
+      </c>
+      <c r="F131" s="4"/>
+      <c r="G131" s="4"/>
     </row>
     <row r="132" ht="259.75" spans="1:7">
       <c r="A132" s="4" t="s">
@@ -7155,14 +7155,14 @@
       <c r="C132" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="D132" s="4" t="s">
+      <c r="D132" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="E132" s="7">
-        <v>1</v>
-      </c>
-      <c r="F132" s="8"/>
-      <c r="G132" s="8"/>
+      <c r="E132" s="8">
+        <v>1</v>
+      </c>
+      <c r="F132" s="4"/>
+      <c r="G132" s="4"/>
     </row>
     <row r="133" ht="198.75" spans="1:7">
       <c r="A133" s="4" t="s">
@@ -7174,14 +7174,14 @@
       <c r="C133" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="D133" s="4" t="s">
+      <c r="D133" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="E133" s="7">
-        <v>1</v>
-      </c>
-      <c r="F133" s="8"/>
-      <c r="G133" s="8"/>
+      <c r="E133" s="8">
+        <v>1</v>
+      </c>
+      <c r="F133" s="4"/>
+      <c r="G133" s="4"/>
     </row>
     <row r="134" ht="137.75" spans="1:7">
       <c r="A134" s="4" t="s">
@@ -7193,14 +7193,14 @@
       <c r="C134" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="D134" s="4" t="s">
+      <c r="D134" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="E134" s="7">
-        <v>1</v>
-      </c>
-      <c r="F134" s="8"/>
-      <c r="G134" s="8"/>
+      <c r="E134" s="8">
+        <v>1</v>
+      </c>
+      <c r="F134" s="4"/>
+      <c r="G134" s="4"/>
     </row>
     <row r="135" ht="107.75" spans="1:7">
       <c r="A135" s="4" t="s">
@@ -7212,14 +7212,14 @@
       <c r="C135" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="D135" s="4" t="s">
+      <c r="D135" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="E135" s="7">
-        <v>1</v>
-      </c>
-      <c r="F135" s="8"/>
-      <c r="G135" s="8"/>
+      <c r="E135" s="8">
+        <v>1</v>
+      </c>
+      <c r="F135" s="4"/>
+      <c r="G135" s="4"/>
     </row>
     <row r="136" ht="228.75" spans="1:7">
       <c r="A136" s="4" t="s">
@@ -7231,14 +7231,14 @@
       <c r="C136" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="D136" s="4" t="s">
+      <c r="D136" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="E136" s="7">
-        <v>1</v>
-      </c>
-      <c r="F136" s="8"/>
-      <c r="G136" s="8"/>
+      <c r="E136" s="8">
+        <v>1</v>
+      </c>
+      <c r="F136" s="4"/>
+      <c r="G136" s="4"/>
     </row>
     <row r="137" ht="183.75" spans="1:7">
       <c r="A137" s="4" t="s">
@@ -7250,14 +7250,14 @@
       <c r="C137" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="D137" s="4" t="s">
+      <c r="D137" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="E137" s="7">
-        <v>1</v>
-      </c>
-      <c r="F137" s="8"/>
-      <c r="G137" s="8"/>
+      <c r="E137" s="8">
+        <v>1</v>
+      </c>
+      <c r="F137" s="4"/>
+      <c r="G137" s="4"/>
     </row>
     <row r="138" ht="152.75" spans="1:7">
       <c r="A138" s="4" t="s">
@@ -7269,14 +7269,14 @@
       <c r="C138" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="D138" s="4" t="s">
+      <c r="D138" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="E138" s="7">
-        <v>1</v>
-      </c>
-      <c r="F138" s="8"/>
-      <c r="G138" s="8"/>
+      <c r="E138" s="8">
+        <v>1</v>
+      </c>
+      <c r="F138" s="4"/>
+      <c r="G138" s="4"/>
     </row>
     <row r="139" ht="92.75" spans="1:7">
       <c r="A139" s="4" t="s">
@@ -7288,14 +7288,14 @@
       <c r="C139" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="D139" s="4" t="s">
+      <c r="D139" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="E139" s="7">
-        <v>1</v>
-      </c>
-      <c r="F139" s="8"/>
-      <c r="G139" s="8"/>
+      <c r="E139" s="8">
+        <v>1</v>
+      </c>
+      <c r="F139" s="4"/>
+      <c r="G139" s="4"/>
     </row>
     <row r="140" ht="92.75" spans="1:7">
       <c r="A140" s="4" t="s">
@@ -7307,33 +7307,33 @@
       <c r="C140" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="D140" s="4" t="s">
+      <c r="D140" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="E140" s="7">
-        <v>1</v>
-      </c>
-      <c r="F140" s="8"/>
-      <c r="G140" s="8"/>
+      <c r="E140" s="8">
+        <v>1</v>
+      </c>
+      <c r="F140" s="4"/>
+      <c r="G140" s="4"/>
     </row>
     <row r="141" ht="107.75" spans="1:7">
       <c r="A141" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="B141" s="5" t="s">
+      <c r="B141" s="6" t="s">
         <v>558</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="D141" s="4" t="s">
+      <c r="D141" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="E141" s="7">
-        <v>1</v>
-      </c>
-      <c r="F141" s="8"/>
-      <c r="G141" s="8"/>
+      <c r="E141" s="8">
+        <v>1</v>
+      </c>
+      <c r="F141" s="4"/>
+      <c r="G141" s="4"/>
     </row>
     <row r="142" ht="122.75" spans="1:7">
       <c r="A142" s="4" t="s">
@@ -7345,14 +7345,14 @@
       <c r="C142" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="D142" s="4" t="s">
+      <c r="D142" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="E142" s="7">
-        <v>1</v>
-      </c>
-      <c r="F142" s="8"/>
-      <c r="G142" s="8"/>
+      <c r="E142" s="8">
+        <v>1</v>
+      </c>
+      <c r="F142" s="4"/>
+      <c r="G142" s="4"/>
     </row>
     <row r="143" ht="107.75" spans="1:7">
       <c r="A143" s="4" t="s">
@@ -7364,14 +7364,14 @@
       <c r="C143" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="D143" s="4" t="s">
+      <c r="D143" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="E143" s="7">
-        <v>1</v>
-      </c>
-      <c r="F143" s="8"/>
-      <c r="G143" s="8"/>
+      <c r="E143" s="8">
+        <v>1</v>
+      </c>
+      <c r="F143" s="4"/>
+      <c r="G143" s="4"/>
     </row>
     <row r="144" ht="244.75" spans="1:7">
       <c r="A144" s="4" t="s">
@@ -7383,14 +7383,14 @@
       <c r="C144" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="D144" s="4" t="s">
+      <c r="D144" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="E144" s="7">
-        <v>1</v>
-      </c>
-      <c r="F144" s="8"/>
-      <c r="G144" s="8"/>
+      <c r="E144" s="8">
+        <v>1</v>
+      </c>
+      <c r="F144" s="4"/>
+      <c r="G144" s="4"/>
     </row>
     <row r="145" ht="213.75" spans="1:7">
       <c r="A145" s="4" t="s">
@@ -7402,14 +7402,14 @@
       <c r="C145" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="D145" s="4" t="s">
+      <c r="D145" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="E145" s="7">
-        <v>1</v>
-      </c>
-      <c r="F145" s="8"/>
-      <c r="G145" s="8"/>
+      <c r="E145" s="8">
+        <v>1</v>
+      </c>
+      <c r="F145" s="4"/>
+      <c r="G145" s="4"/>
     </row>
     <row r="146" ht="92.75" spans="1:7">
       <c r="A146" s="4" t="s">
@@ -7421,14 +7421,14 @@
       <c r="C146" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="D146" s="4" t="s">
+      <c r="D146" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="E146" s="7">
-        <v>1</v>
-      </c>
-      <c r="F146" s="8"/>
-      <c r="G146" s="8"/>
+      <c r="E146" s="8">
+        <v>1</v>
+      </c>
+      <c r="F146" s="4"/>
+      <c r="G146" s="4"/>
     </row>
     <row r="147" ht="92.75" spans="1:7">
       <c r="A147" s="4" t="s">
@@ -7440,14 +7440,14 @@
       <c r="C147" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="D147" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="E147" s="7">
-        <v>1</v>
-      </c>
-      <c r="F147" s="8"/>
-      <c r="G147" s="8"/>
+      <c r="E147" s="8">
+        <v>1</v>
+      </c>
+      <c r="F147" s="4"/>
+      <c r="G147" s="4"/>
     </row>
     <row r="148" ht="137.75" spans="1:7">
       <c r="A148" s="4" t="s">
@@ -7459,14 +7459,14 @@
       <c r="C148" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="D148" s="4" t="s">
+      <c r="D148" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="E148" s="7">
-        <v>1</v>
-      </c>
-      <c r="F148" s="8"/>
-      <c r="G148" s="8"/>
+      <c r="E148" s="8">
+        <v>1</v>
+      </c>
+      <c r="F148" s="4"/>
+      <c r="G148" s="4"/>
     </row>
     <row r="149" ht="92.75" spans="1:7">
       <c r="A149" s="4" t="s">
@@ -7478,14 +7478,14 @@
       <c r="C149" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="D149" s="4" t="s">
+      <c r="D149" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="E149" s="7">
-        <v>1</v>
-      </c>
-      <c r="F149" s="8"/>
-      <c r="G149" s="8"/>
+      <c r="E149" s="8">
+        <v>1</v>
+      </c>
+      <c r="F149" s="4"/>
+      <c r="G149" s="4"/>
     </row>
     <row r="150" ht="274.75" spans="1:7">
       <c r="A150" s="4" t="s">
@@ -7497,14 +7497,14 @@
       <c r="C150" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="D150" s="4" t="s">
+      <c r="D150" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="E150" s="7">
-        <v>1</v>
-      </c>
-      <c r="F150" s="8"/>
-      <c r="G150" s="8"/>
+      <c r="E150" s="8">
+        <v>1</v>
+      </c>
+      <c r="F150" s="4"/>
+      <c r="G150" s="4"/>
     </row>
     <row r="151" ht="168.75" spans="1:7">
       <c r="A151" s="4" t="s">
@@ -7516,14 +7516,14 @@
       <c r="C151" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="D151" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="E151" s="7">
-        <v>1</v>
-      </c>
-      <c r="F151" s="8"/>
-      <c r="G151" s="8"/>
+      <c r="E151" s="8">
+        <v>1</v>
+      </c>
+      <c r="F151" s="4"/>
+      <c r="G151" s="4"/>
     </row>
     <row r="152" ht="168.75" spans="1:7">
       <c r="A152" s="4" t="s">
@@ -7535,14 +7535,14 @@
       <c r="C152" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="D152" s="4" t="s">
+      <c r="D152" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="E152" s="7">
-        <v>1</v>
-      </c>
-      <c r="F152" s="8"/>
-      <c r="G152" s="8"/>
+      <c r="E152" s="8">
+        <v>1</v>
+      </c>
+      <c r="F152" s="4"/>
+      <c r="G152" s="4"/>
     </row>
     <row r="153" ht="122.75" spans="1:7">
       <c r="A153" s="4" t="s">
@@ -7554,33 +7554,33 @@
       <c r="C153" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="D153" s="4" t="s">
+      <c r="D153" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="E153" s="7">
-        <v>1</v>
-      </c>
-      <c r="F153" s="8"/>
-      <c r="G153" s="8"/>
+      <c r="E153" s="8">
+        <v>1</v>
+      </c>
+      <c r="F153" s="4"/>
+      <c r="G153" s="4"/>
     </row>
     <row r="154" ht="107.75" spans="1:7">
       <c r="A154" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="B154" s="5" t="s">
+      <c r="B154" s="6" t="s">
         <v>610</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="D154" s="4" t="s">
+      <c r="D154" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="E154" s="7">
-        <v>1</v>
-      </c>
-      <c r="F154" s="8"/>
-      <c r="G154" s="8"/>
+      <c r="E154" s="8">
+        <v>1</v>
+      </c>
+      <c r="F154" s="4"/>
+      <c r="G154" s="4"/>
     </row>
     <row r="155" ht="107.75" spans="1:7">
       <c r="A155" s="4" t="s">
@@ -7592,14 +7592,14 @@
       <c r="C155" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="D155" s="4" t="s">
+      <c r="D155" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="E155" s="7">
-        <v>1</v>
-      </c>
-      <c r="F155" s="8"/>
-      <c r="G155" s="8"/>
+      <c r="E155" s="8">
+        <v>1</v>
+      </c>
+      <c r="F155" s="4"/>
+      <c r="G155" s="4"/>
     </row>
     <row r="156" ht="198.75" spans="1:7">
       <c r="A156" s="4" t="s">
@@ -7611,14 +7611,14 @@
       <c r="C156" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="D156" s="4" t="s">
+      <c r="D156" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="E156" s="7">
-        <v>1</v>
-      </c>
-      <c r="F156" s="8"/>
-      <c r="G156" s="8"/>
+      <c r="E156" s="8">
+        <v>1</v>
+      </c>
+      <c r="F156" s="4"/>
+      <c r="G156" s="4"/>
     </row>
     <row r="157" ht="92.75" spans="1:7">
       <c r="A157" s="4" t="s">
@@ -7630,14 +7630,14 @@
       <c r="C157" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="D157" s="4" t="s">
+      <c r="D157" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="E157" s="7">
-        <v>1</v>
-      </c>
-      <c r="F157" s="8"/>
-      <c r="G157" s="8"/>
+      <c r="E157" s="8">
+        <v>1</v>
+      </c>
+      <c r="F157" s="4"/>
+      <c r="G157" s="4"/>
     </row>
     <row r="158" ht="107.75" spans="1:7">
       <c r="A158" s="4" t="s">
@@ -7649,14 +7649,14 @@
       <c r="C158" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="D158" s="4" t="s">
+      <c r="D158" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="E158" s="7">
-        <v>1</v>
-      </c>
-      <c r="F158" s="8"/>
-      <c r="G158" s="8"/>
+      <c r="E158" s="8">
+        <v>1</v>
+      </c>
+      <c r="F158" s="4"/>
+      <c r="G158" s="4"/>
     </row>
     <row r="159" ht="198.75" spans="1:7">
       <c r="A159" s="4" t="s">
@@ -7668,14 +7668,14 @@
       <c r="C159" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D159" s="4" t="s">
+      <c r="D159" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="E159" s="7">
-        <v>1</v>
-      </c>
-      <c r="F159" s="8"/>
-      <c r="G159" s="8"/>
+      <c r="E159" s="8">
+        <v>1</v>
+      </c>
+      <c r="F159" s="4"/>
+      <c r="G159" s="4"/>
     </row>
     <row r="160" ht="137.75" spans="1:7">
       <c r="A160" s="4" t="s">
@@ -7687,14 +7687,14 @@
       <c r="C160" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="D160" s="4" t="s">
+      <c r="D160" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="E160" s="7">
-        <v>1</v>
-      </c>
-      <c r="F160" s="8"/>
-      <c r="G160" s="8"/>
+      <c r="E160" s="8">
+        <v>1</v>
+      </c>
+      <c r="F160" s="4"/>
+      <c r="G160" s="4"/>
     </row>
     <row r="161" ht="122.75" spans="1:7">
       <c r="A161" s="4" t="s">
@@ -7706,14 +7706,14 @@
       <c r="C161" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="D161" s="4" t="s">
+      <c r="D161" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="E161" s="7">
-        <v>1</v>
-      </c>
-      <c r="F161" s="8"/>
-      <c r="G161" s="8"/>
+      <c r="E161" s="8">
+        <v>1</v>
+      </c>
+      <c r="F161" s="4"/>
+      <c r="G161" s="4"/>
     </row>
     <row r="162" ht="107.75" spans="1:7">
       <c r="A162" s="4" t="s">
@@ -7725,14 +7725,14 @@
       <c r="C162" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="D162" s="4" t="s">
+      <c r="D162" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="E162" s="7">
-        <v>1</v>
-      </c>
-      <c r="F162" s="8"/>
-      <c r="G162" s="8"/>
+      <c r="E162" s="8">
+        <v>1</v>
+      </c>
+      <c r="F162" s="4"/>
+      <c r="G162" s="4"/>
     </row>
     <row r="163" ht="92.75" spans="1:7">
       <c r="A163" s="4" t="s">
@@ -7744,14 +7744,14 @@
       <c r="C163" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="D163" s="4" t="s">
+      <c r="D163" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="E163" s="7">
-        <v>1</v>
-      </c>
-      <c r="F163" s="8"/>
-      <c r="G163" s="8"/>
+      <c r="E163" s="8">
+        <v>1</v>
+      </c>
+      <c r="F163" s="4"/>
+      <c r="G163" s="4"/>
     </row>
     <row r="164" ht="244.75" spans="1:7">
       <c r="A164" s="4" t="s">
@@ -7763,33 +7763,33 @@
       <c r="C164" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="D164" s="4" t="s">
+      <c r="D164" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="E164" s="7">
-        <v>1</v>
-      </c>
-      <c r="F164" s="8"/>
-      <c r="G164" s="8"/>
+      <c r="E164" s="8">
+        <v>1</v>
+      </c>
+      <c r="F164" s="4"/>
+      <c r="G164" s="4"/>
     </row>
     <row r="165" ht="122.75" spans="1:7">
       <c r="A165" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="B165" s="5" t="s">
+      <c r="B165" s="6" t="s">
         <v>654</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="D165" s="4" t="s">
+      <c r="D165" s="5" t="s">
         <v>656</v>
       </c>
-      <c r="E165" s="7">
-        <v>1</v>
-      </c>
-      <c r="F165" s="8"/>
-      <c r="G165" s="8"/>
+      <c r="E165" s="8">
+        <v>1</v>
+      </c>
+      <c r="F165" s="4"/>
+      <c r="G165" s="4"/>
     </row>
     <row r="166" ht="107.75" spans="1:7">
       <c r="A166" s="4" t="s">
@@ -7801,14 +7801,14 @@
       <c r="C166" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="D166" s="4" t="s">
+      <c r="D166" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="E166" s="7">
-        <v>1</v>
-      </c>
-      <c r="F166" s="8"/>
-      <c r="G166" s="8"/>
+      <c r="E166" s="8">
+        <v>1</v>
+      </c>
+      <c r="F166" s="4"/>
+      <c r="G166" s="4"/>
     </row>
     <row r="167" ht="137.75" spans="1:7">
       <c r="A167" s="4" t="s">
@@ -7820,14 +7820,14 @@
       <c r="C167" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="D167" s="4" t="s">
+      <c r="D167" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="E167" s="7">
-        <v>1</v>
-      </c>
-      <c r="F167" s="8"/>
-      <c r="G167" s="8"/>
+      <c r="E167" s="8">
+        <v>1</v>
+      </c>
+      <c r="F167" s="4"/>
+      <c r="G167" s="4"/>
     </row>
     <row r="168" ht="107.75" spans="1:7">
       <c r="A168" s="4" t="s">
@@ -7839,14 +7839,14 @@
       <c r="C168" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="D168" s="4" t="s">
+      <c r="D168" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="E168" s="7">
-        <v>1</v>
-      </c>
-      <c r="F168" s="8"/>
-      <c r="G168" s="8"/>
+      <c r="E168" s="8">
+        <v>1</v>
+      </c>
+      <c r="F168" s="4"/>
+      <c r="G168" s="4"/>
     </row>
     <row r="169" ht="259.75" spans="1:7">
       <c r="A169" s="4" t="s">
@@ -7858,14 +7858,14 @@
       <c r="C169" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="D169" s="4" t="s">
+      <c r="D169" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="E169" s="7">
-        <v>1</v>
-      </c>
-      <c r="F169" s="8"/>
-      <c r="G169" s="8"/>
+      <c r="E169" s="8">
+        <v>1</v>
+      </c>
+      <c r="F169" s="4"/>
+      <c r="G169" s="4"/>
     </row>
     <row r="170" ht="122.75" spans="1:7">
       <c r="A170" s="4" t="s">
@@ -7877,14 +7877,14 @@
       <c r="C170" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="D170" s="4" t="s">
+      <c r="D170" s="5" t="s">
         <v>676</v>
       </c>
-      <c r="E170" s="7">
-        <v>1</v>
-      </c>
-      <c r="F170" s="8"/>
-      <c r="G170" s="8"/>
+      <c r="E170" s="8">
+        <v>1</v>
+      </c>
+      <c r="F170" s="4"/>
+      <c r="G170" s="4"/>
     </row>
     <row r="171" ht="168.75" spans="1:7">
       <c r="A171" s="4" t="s">
@@ -7896,14 +7896,14 @@
       <c r="C171" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="D171" s="4" t="s">
+      <c r="D171" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="E171" s="7">
-        <v>1</v>
-      </c>
-      <c r="F171" s="8"/>
-      <c r="G171" s="8"/>
+      <c r="E171" s="8">
+        <v>1</v>
+      </c>
+      <c r="F171" s="4"/>
+      <c r="G171" s="4"/>
     </row>
     <row r="172" ht="168.75" spans="1:7">
       <c r="A172" s="4" t="s">
@@ -7915,14 +7915,14 @@
       <c r="C172" s="4" t="s">
         <v>683</v>
       </c>
-      <c r="D172" s="4" t="s">
+      <c r="D172" s="5" t="s">
         <v>684</v>
       </c>
-      <c r="E172" s="7">
-        <v>1</v>
-      </c>
-      <c r="F172" s="8"/>
-      <c r="G172" s="8"/>
+      <c r="E172" s="8">
+        <v>1</v>
+      </c>
+      <c r="F172" s="4"/>
+      <c r="G172" s="4"/>
     </row>
     <row r="173" ht="92.75" spans="1:7">
       <c r="A173" s="4" t="s">
@@ -7934,14 +7934,14 @@
       <c r="C173" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="D173" s="4" t="s">
+      <c r="D173" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="E173" s="7">
-        <v>1</v>
-      </c>
-      <c r="F173" s="8"/>
-      <c r="G173" s="8"/>
+      <c r="E173" s="8">
+        <v>1</v>
+      </c>
+      <c r="F173" s="4"/>
+      <c r="G173" s="4"/>
     </row>
     <row r="174" ht="107.75" spans="1:7">
       <c r="A174" s="4" t="s">
@@ -7953,14 +7953,14 @@
       <c r="C174" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="D174" s="4" t="s">
+      <c r="D174" s="5" t="s">
         <v>692</v>
       </c>
-      <c r="E174" s="7">
-        <v>1</v>
-      </c>
-      <c r="F174" s="8"/>
-      <c r="G174" s="8"/>
+      <c r="E174" s="8">
+        <v>1</v>
+      </c>
+      <c r="F174" s="4"/>
+      <c r="G174" s="4"/>
     </row>
     <row r="175" ht="137.75" spans="1:7">
       <c r="A175" s="4" t="s">
@@ -7972,14 +7972,14 @@
       <c r="C175" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="D175" s="4" t="s">
+      <c r="D175" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="E175" s="7">
-        <v>1</v>
-      </c>
-      <c r="F175" s="8"/>
-      <c r="G175" s="8"/>
+      <c r="E175" s="8">
+        <v>1</v>
+      </c>
+      <c r="F175" s="4"/>
+      <c r="G175" s="4"/>
     </row>
     <row r="176" ht="107.75" spans="1:7">
       <c r="A176" s="4" t="s">
@@ -7991,14 +7991,14 @@
       <c r="C176" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="D176" s="4" t="s">
+      <c r="D176" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="E176" s="7">
-        <v>1</v>
-      </c>
-      <c r="F176" s="8"/>
-      <c r="G176" s="8"/>
+      <c r="E176" s="8">
+        <v>1</v>
+      </c>
+      <c r="F176" s="4"/>
+      <c r="G176" s="4"/>
     </row>
     <row r="177" ht="92.75" spans="1:7">
       <c r="A177" s="4" t="s">
@@ -8010,14 +8010,14 @@
       <c r="C177" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="D177" s="4" t="s">
+      <c r="D177" s="5" t="s">
         <v>704</v>
       </c>
-      <c r="E177" s="7">
-        <v>1</v>
-      </c>
-      <c r="F177" s="8"/>
-      <c r="G177" s="8"/>
+      <c r="E177" s="8">
+        <v>1</v>
+      </c>
+      <c r="F177" s="4"/>
+      <c r="G177" s="4"/>
     </row>
     <row r="178" ht="198.75" spans="1:7">
       <c r="A178" s="4" t="s">
@@ -8029,14 +8029,14 @@
       <c r="C178" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="D178" s="4" t="s">
+      <c r="D178" s="5" t="s">
         <v>708</v>
       </c>
-      <c r="E178" s="7">
-        <v>1</v>
-      </c>
-      <c r="F178" s="8"/>
-      <c r="G178" s="8"/>
+      <c r="E178" s="8">
+        <v>1</v>
+      </c>
+      <c r="F178" s="4"/>
+      <c r="G178" s="4"/>
     </row>
     <row r="179" ht="107.75" spans="1:7">
       <c r="A179" s="4" t="s">
@@ -8048,14 +8048,14 @@
       <c r="C179" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="D179" s="4" t="s">
+      <c r="D179" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="E179" s="7">
-        <v>1</v>
-      </c>
-      <c r="F179" s="8"/>
-      <c r="G179" s="8"/>
+      <c r="E179" s="8">
+        <v>1</v>
+      </c>
+      <c r="F179" s="4"/>
+      <c r="G179" s="4"/>
     </row>
     <row r="180" ht="259.75" spans="1:7">
       <c r="A180" s="4" t="s">
@@ -8067,14 +8067,14 @@
       <c r="C180" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="D180" s="4" t="s">
+      <c r="D180" s="5" t="s">
         <v>716</v>
       </c>
-      <c r="E180" s="7">
-        <v>1</v>
-      </c>
-      <c r="F180" s="8"/>
-      <c r="G180" s="8"/>
+      <c r="E180" s="8">
+        <v>1</v>
+      </c>
+      <c r="F180" s="4"/>
+      <c r="G180" s="4"/>
     </row>
     <row r="181" ht="183.75" spans="1:7">
       <c r="A181" s="4" t="s">
@@ -8086,14 +8086,14 @@
       <c r="C181" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="D181" s="4" t="s">
+      <c r="D181" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="E181" s="7">
-        <v>1</v>
-      </c>
-      <c r="F181" s="8"/>
-      <c r="G181" s="8"/>
+      <c r="E181" s="8">
+        <v>1</v>
+      </c>
+      <c r="F181" s="4"/>
+      <c r="G181" s="4"/>
     </row>
     <row r="182" ht="213.75" spans="1:7">
       <c r="A182" s="4" t="s">
@@ -8105,14 +8105,14 @@
       <c r="C182" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="D182" s="4" t="s">
+      <c r="D182" s="5" t="s">
         <v>724</v>
       </c>
-      <c r="E182" s="7">
-        <v>1</v>
-      </c>
-      <c r="F182" s="8"/>
-      <c r="G182" s="8"/>
+      <c r="E182" s="8">
+        <v>1</v>
+      </c>
+      <c r="F182" s="4"/>
+      <c r="G182" s="4"/>
     </row>
     <row r="183" ht="183.75" spans="1:7">
       <c r="A183" s="4" t="s">
@@ -8124,14 +8124,14 @@
       <c r="C183" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="D183" s="4" t="s">
+      <c r="D183" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="E183" s="7">
-        <v>1</v>
-      </c>
-      <c r="F183" s="8"/>
-      <c r="G183" s="8"/>
+      <c r="E183" s="8">
+        <v>1</v>
+      </c>
+      <c r="F183" s="4"/>
+      <c r="G183" s="4"/>
     </row>
     <row r="184" ht="122.75" spans="1:7">
       <c r="A184" s="4" t="s">
@@ -8143,33 +8143,33 @@
       <c r="C184" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="D184" s="4" t="s">
+      <c r="D184" s="5" t="s">
         <v>732</v>
       </c>
-      <c r="E184" s="7">
-        <v>1</v>
-      </c>
-      <c r="F184" s="8"/>
-      <c r="G184" s="8"/>
+      <c r="E184" s="8">
+        <v>1</v>
+      </c>
+      <c r="F184" s="4"/>
+      <c r="G184" s="4"/>
     </row>
     <row r="185" ht="122.75" spans="1:7">
       <c r="A185" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="B185" s="5" t="s">
+      <c r="B185" s="6" t="s">
         <v>734</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="D185" s="4" t="s">
+      <c r="D185" s="5" t="s">
         <v>736</v>
       </c>
-      <c r="E185" s="7">
-        <v>1</v>
-      </c>
-      <c r="F185" s="8"/>
-      <c r="G185" s="8"/>
+      <c r="E185" s="8">
+        <v>1</v>
+      </c>
+      <c r="F185" s="4"/>
+      <c r="G185" s="4"/>
     </row>
     <row r="186" ht="107.75" spans="1:7">
       <c r="A186" s="4" t="s">
@@ -8181,14 +8181,14 @@
       <c r="C186" s="4" t="s">
         <v>739</v>
       </c>
-      <c r="D186" s="4" t="s">
+      <c r="D186" s="5" t="s">
         <v>740</v>
       </c>
-      <c r="E186" s="7">
-        <v>1</v>
-      </c>
-      <c r="F186" s="8"/>
-      <c r="G186" s="8"/>
+      <c r="E186" s="8">
+        <v>1</v>
+      </c>
+      <c r="F186" s="4"/>
+      <c r="G186" s="4"/>
     </row>
     <row r="187" ht="122.75" spans="1:7">
       <c r="A187" s="4" t="s">
@@ -8200,33 +8200,33 @@
       <c r="C187" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="D187" s="4" t="s">
+      <c r="D187" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="E187" s="7">
-        <v>1</v>
-      </c>
-      <c r="F187" s="8"/>
-      <c r="G187" s="8"/>
+      <c r="E187" s="8">
+        <v>1</v>
+      </c>
+      <c r="F187" s="4"/>
+      <c r="G187" s="4"/>
     </row>
     <row r="188" ht="107.75" spans="1:7">
       <c r="A188" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="B188" s="5" t="s">
+      <c r="B188" s="6" t="s">
         <v>746</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>747</v>
       </c>
-      <c r="D188" s="4" t="s">
+      <c r="D188" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="E188" s="7">
-        <v>1</v>
-      </c>
-      <c r="F188" s="8"/>
-      <c r="G188" s="8"/>
+      <c r="E188" s="8">
+        <v>1</v>
+      </c>
+      <c r="F188" s="4"/>
+      <c r="G188" s="4"/>
     </row>
     <row r="189" ht="92.75" spans="1:7">
       <c r="A189" s="4" t="s">
@@ -8238,14 +8238,14 @@
       <c r="C189" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="D189" s="4" t="s">
+      <c r="D189" s="5" t="s">
         <v>752</v>
       </c>
-      <c r="E189" s="7">
-        <v>1</v>
-      </c>
-      <c r="F189" s="8"/>
-      <c r="G189" s="8"/>
+      <c r="E189" s="8">
+        <v>1</v>
+      </c>
+      <c r="F189" s="4"/>
+      <c r="G189" s="4"/>
     </row>
     <row r="190" ht="183.75" spans="1:7">
       <c r="A190" s="4" t="s">
@@ -8257,14 +8257,14 @@
       <c r="C190" s="4" t="s">
         <v>755</v>
       </c>
-      <c r="D190" s="4" t="s">
+      <c r="D190" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="E190" s="7">
-        <v>1</v>
-      </c>
-      <c r="F190" s="8"/>
-      <c r="G190" s="8"/>
+      <c r="E190" s="8">
+        <v>1</v>
+      </c>
+      <c r="F190" s="4"/>
+      <c r="G190" s="4"/>
     </row>
     <row r="191" ht="137.75" spans="1:7">
       <c r="A191" s="4" t="s">
@@ -8276,14 +8276,14 @@
       <c r="C191" s="4" t="s">
         <v>759</v>
       </c>
-      <c r="D191" s="4" t="s">
+      <c r="D191" s="5" t="s">
         <v>760</v>
       </c>
-      <c r="E191" s="7">
-        <v>1</v>
-      </c>
-      <c r="F191" s="8"/>
-      <c r="G191" s="8"/>
+      <c r="E191" s="8">
+        <v>1</v>
+      </c>
+      <c r="F191" s="4"/>
+      <c r="G191" s="4"/>
     </row>
     <row r="192" ht="107.75" spans="1:7">
       <c r="A192" s="4" t="s">
@@ -8295,14 +8295,14 @@
       <c r="C192" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="D192" s="4" t="s">
+      <c r="D192" s="5" t="s">
         <v>764</v>
       </c>
-      <c r="E192" s="7">
-        <v>1</v>
-      </c>
-      <c r="F192" s="8"/>
-      <c r="G192" s="8"/>
+      <c r="E192" s="8">
+        <v>1</v>
+      </c>
+      <c r="F192" s="4"/>
+      <c r="G192" s="4"/>
     </row>
     <row r="193" ht="107.75" spans="1:7">
       <c r="A193" s="4" t="s">
@@ -8314,14 +8314,14 @@
       <c r="C193" s="4" t="s">
         <v>767</v>
       </c>
-      <c r="D193" s="4" t="s">
+      <c r="D193" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="E193" s="7">
-        <v>1</v>
-      </c>
-      <c r="F193" s="8"/>
-      <c r="G193" s="8"/>
+      <c r="E193" s="8">
+        <v>1</v>
+      </c>
+      <c r="F193" s="4"/>
+      <c r="G193" s="4"/>
     </row>
     <row r="194" ht="107.75" spans="1:7">
       <c r="A194" s="4" t="s">
@@ -8333,14 +8333,14 @@
       <c r="C194" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="D194" s="4" t="s">
+      <c r="D194" s="5" t="s">
         <v>772</v>
       </c>
-      <c r="E194" s="7">
-        <v>1</v>
-      </c>
-      <c r="F194" s="8"/>
-      <c r="G194" s="8"/>
+      <c r="E194" s="8">
+        <v>1</v>
+      </c>
+      <c r="F194" s="4"/>
+      <c r="G194" s="4"/>
     </row>
     <row r="195" ht="137.75" spans="1:7">
       <c r="A195" s="4" t="s">
@@ -8352,14 +8352,14 @@
       <c r="C195" s="4" t="s">
         <v>775</v>
       </c>
-      <c r="D195" s="4" t="s">
+      <c r="D195" s="5" t="s">
         <v>776</v>
       </c>
-      <c r="E195" s="7">
-        <v>1</v>
-      </c>
-      <c r="F195" s="8"/>
-      <c r="G195" s="8"/>
+      <c r="E195" s="8">
+        <v>1</v>
+      </c>
+      <c r="F195" s="4"/>
+      <c r="G195" s="4"/>
     </row>
     <row r="196" ht="107.75" spans="1:7">
       <c r="A196" s="4" t="s">
@@ -8371,14 +8371,14 @@
       <c r="C196" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="D196" s="4" t="s">
+      <c r="D196" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="E196" s="7">
-        <v>1</v>
-      </c>
-      <c r="F196" s="8"/>
-      <c r="G196" s="8"/>
+      <c r="E196" s="8">
+        <v>1</v>
+      </c>
+      <c r="F196" s="4"/>
+      <c r="G196" s="4"/>
     </row>
     <row r="197" ht="92.75" spans="1:7">
       <c r="A197" s="4" t="s">
@@ -8390,14 +8390,14 @@
       <c r="C197" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="D197" s="4" t="s">
+      <c r="D197" s="5" t="s">
         <v>784</v>
       </c>
-      <c r="E197" s="7">
-        <v>1</v>
-      </c>
-      <c r="F197" s="8"/>
-      <c r="G197" s="8"/>
+      <c r="E197" s="8">
+        <v>1</v>
+      </c>
+      <c r="F197" s="4"/>
+      <c r="G197" s="4"/>
     </row>
     <row r="198" ht="107.75" spans="1:7">
       <c r="A198" s="4" t="s">
@@ -8409,14 +8409,14 @@
       <c r="C198" s="4" t="s">
         <v>787</v>
       </c>
-      <c r="D198" s="4" t="s">
+      <c r="D198" s="5" t="s">
         <v>788</v>
       </c>
-      <c r="E198" s="7">
-        <v>1</v>
-      </c>
-      <c r="F198" s="8"/>
-      <c r="G198" s="8"/>
+      <c r="E198" s="8">
+        <v>1</v>
+      </c>
+      <c r="F198" s="4"/>
+      <c r="G198" s="4"/>
     </row>
     <row r="199" ht="107.75" spans="1:7">
       <c r="A199" s="4" t="s">
@@ -8428,14 +8428,14 @@
       <c r="C199" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="D199" s="4" t="s">
+      <c r="D199" s="5" t="s">
         <v>792</v>
       </c>
-      <c r="E199" s="7">
-        <v>1</v>
-      </c>
-      <c r="F199" s="8"/>
-      <c r="G199" s="8"/>
+      <c r="E199" s="8">
+        <v>1</v>
+      </c>
+      <c r="F199" s="4"/>
+      <c r="G199" s="4"/>
     </row>
     <row r="200" ht="198.75" spans="1:7">
       <c r="A200" s="4" t="s">
@@ -8447,14 +8447,14 @@
       <c r="C200" s="4" t="s">
         <v>795</v>
       </c>
-      <c r="D200" s="4" t="s">
+      <c r="D200" s="5" t="s">
         <v>796</v>
       </c>
-      <c r="E200" s="7">
-        <v>1</v>
-      </c>
-      <c r="F200" s="8"/>
-      <c r="G200" s="8"/>
+      <c r="E200" s="8">
+        <v>1</v>
+      </c>
+      <c r="F200" s="4"/>
+      <c r="G200" s="4"/>
     </row>
     <row r="201" ht="92.75" spans="1:7">
       <c r="A201" s="4" t="s">
@@ -8466,14 +8466,14 @@
       <c r="C201" s="4" t="s">
         <v>799</v>
       </c>
-      <c r="D201" s="4" t="s">
+      <c r="D201" s="5" t="s">
         <v>800</v>
       </c>
-      <c r="E201" s="7">
-        <v>1</v>
-      </c>
-      <c r="F201" s="8"/>
-      <c r="G201" s="8"/>
+      <c r="E201" s="8">
+        <v>1</v>
+      </c>
+      <c r="F201" s="4"/>
+      <c r="G201" s="4"/>
     </row>
     <row r="202" ht="198.75" spans="1:7">
       <c r="A202" s="4" t="s">
@@ -8485,14 +8485,14 @@
       <c r="C202" s="4" t="s">
         <v>803</v>
       </c>
-      <c r="D202" s="4" t="s">
+      <c r="D202" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="E202" s="7">
-        <v>1</v>
-      </c>
-      <c r="F202" s="8"/>
-      <c r="G202" s="8"/>
+      <c r="E202" s="8">
+        <v>1</v>
+      </c>
+      <c r="F202" s="4"/>
+      <c r="G202" s="4"/>
     </row>
     <row r="203" ht="122.75" spans="1:7">
       <c r="A203" s="4" t="s">
@@ -8504,14 +8504,14 @@
       <c r="C203" s="4" t="s">
         <v>807</v>
       </c>
-      <c r="D203" s="4" t="s">
+      <c r="D203" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="E203" s="7">
-        <v>1</v>
-      </c>
-      <c r="F203" s="8"/>
-      <c r="G203" s="8"/>
+      <c r="E203" s="8">
+        <v>1</v>
+      </c>
+      <c r="F203" s="4"/>
+      <c r="G203" s="4"/>
     </row>
     <row r="204" ht="107.75" spans="1:7">
       <c r="A204" s="4" t="s">
@@ -8523,14 +8523,14 @@
       <c r="C204" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="D204" s="4" t="s">
+      <c r="D204" s="5" t="s">
         <v>812</v>
       </c>
-      <c r="E204" s="7">
-        <v>1</v>
-      </c>
-      <c r="F204" s="8"/>
-      <c r="G204" s="8"/>
+      <c r="E204" s="8">
+        <v>1</v>
+      </c>
+      <c r="F204" s="4"/>
+      <c r="G204" s="4"/>
     </row>
     <row r="205" ht="107.75" spans="1:7">
       <c r="A205" s="4" t="s">
@@ -8542,14 +8542,14 @@
       <c r="C205" s="4" t="s">
         <v>815</v>
       </c>
-      <c r="D205" s="4" t="s">
+      <c r="D205" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="E205" s="7">
-        <v>1</v>
-      </c>
-      <c r="F205" s="8"/>
-      <c r="G205" s="8"/>
+      <c r="E205" s="8">
+        <v>1</v>
+      </c>
+      <c r="F205" s="4"/>
+      <c r="G205" s="4"/>
     </row>
     <row r="206" ht="92.75" spans="1:7">
       <c r="A206" s="4" t="s">
@@ -8561,14 +8561,14 @@
       <c r="C206" s="4" t="s">
         <v>819</v>
       </c>
-      <c r="D206" s="4" t="s">
+      <c r="D206" s="5" t="s">
         <v>820</v>
       </c>
-      <c r="E206" s="7">
-        <v>1</v>
-      </c>
-      <c r="F206" s="8"/>
-      <c r="G206" s="8"/>
+      <c r="E206" s="8">
+        <v>1</v>
+      </c>
+      <c r="F206" s="4"/>
+      <c r="G206" s="4"/>
     </row>
     <row r="207" ht="92.75" spans="1:7">
       <c r="A207" s="4" t="s">
@@ -8580,14 +8580,14 @@
       <c r="C207" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="D207" s="4" t="s">
+      <c r="D207" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="E207" s="7">
-        <v>1</v>
-      </c>
-      <c r="F207" s="8"/>
-      <c r="G207" s="8"/>
+      <c r="E207" s="8">
+        <v>1</v>
+      </c>
+      <c r="F207" s="4"/>
+      <c r="G207" s="4"/>
     </row>
     <row r="208" ht="107.75" spans="1:7">
       <c r="A208" s="4" t="s">
@@ -8599,14 +8599,14 @@
       <c r="C208" s="4" t="s">
         <v>827</v>
       </c>
-      <c r="D208" s="4" t="s">
+      <c r="D208" s="5" t="s">
         <v>828</v>
       </c>
-      <c r="E208" s="7">
-        <v>1</v>
-      </c>
-      <c r="F208" s="8"/>
-      <c r="G208" s="8"/>
+      <c r="E208" s="8">
+        <v>1</v>
+      </c>
+      <c r="F208" s="4"/>
+      <c r="G208" s="4"/>
     </row>
     <row r="209" ht="107.75" spans="1:7">
       <c r="A209" s="4" t="s">
@@ -8618,14 +8618,14 @@
       <c r="C209" s="4" t="s">
         <v>831</v>
       </c>
-      <c r="D209" s="4" t="s">
+      <c r="D209" s="5" t="s">
         <v>832</v>
       </c>
-      <c r="E209" s="7">
-        <v>1</v>
-      </c>
-      <c r="F209" s="8"/>
-      <c r="G209" s="8"/>
+      <c r="E209" s="8">
+        <v>1</v>
+      </c>
+      <c r="F209" s="4"/>
+      <c r="G209" s="4"/>
     </row>
     <row r="210" ht="259.75" spans="1:7">
       <c r="A210" s="4" t="s">
@@ -8637,14 +8637,14 @@
       <c r="C210" s="4" t="s">
         <v>835</v>
       </c>
-      <c r="D210" s="4" t="s">
+      <c r="D210" s="5" t="s">
         <v>836</v>
       </c>
-      <c r="E210" s="7">
-        <v>1</v>
-      </c>
-      <c r="F210" s="8"/>
-      <c r="G210" s="8"/>
+      <c r="E210" s="8">
+        <v>1</v>
+      </c>
+      <c r="F210" s="4"/>
+      <c r="G210" s="4"/>
     </row>
     <row r="211" ht="152.75" spans="1:7">
       <c r="A211" s="4" t="s">
@@ -8656,14 +8656,14 @@
       <c r="C211" s="4" t="s">
         <v>839</v>
       </c>
-      <c r="D211" s="4" t="s">
+      <c r="D211" s="5" t="s">
         <v>840</v>
       </c>
-      <c r="E211" s="7">
-        <v>1</v>
-      </c>
-      <c r="F211" s="8"/>
-      <c r="G211" s="8"/>
+      <c r="E211" s="8">
+        <v>1</v>
+      </c>
+      <c r="F211" s="4"/>
+      <c r="G211" s="4"/>
     </row>
     <row r="212" ht="107.75" spans="1:7">
       <c r="A212" s="4" t="s">
@@ -8675,14 +8675,14 @@
       <c r="C212" s="4" t="s">
         <v>843</v>
       </c>
-      <c r="D212" s="4" t="s">
+      <c r="D212" s="5" t="s">
         <v>844</v>
       </c>
-      <c r="E212" s="7">
-        <v>1</v>
-      </c>
-      <c r="F212" s="8"/>
-      <c r="G212" s="8"/>
+      <c r="E212" s="8">
+        <v>1</v>
+      </c>
+      <c r="F212" s="4"/>
+      <c r="G212" s="4"/>
     </row>
     <row r="213" ht="92.75" spans="1:7">
       <c r="A213" s="4" t="s">
@@ -8694,33 +8694,33 @@
       <c r="C213" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="D213" s="4" t="s">
+      <c r="D213" s="5" t="s">
         <v>848</v>
       </c>
-      <c r="E213" s="7">
-        <v>1</v>
-      </c>
-      <c r="F213" s="8"/>
-      <c r="G213" s="8"/>
+      <c r="E213" s="8">
+        <v>1</v>
+      </c>
+      <c r="F213" s="4"/>
+      <c r="G213" s="4"/>
     </row>
     <row r="214" ht="168.75" spans="1:7">
       <c r="A214" s="4" t="s">
         <v>849</v>
       </c>
-      <c r="B214" s="5" t="s">
+      <c r="B214" s="6" t="s">
         <v>850</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>851</v>
       </c>
-      <c r="D214" s="4" t="s">
+      <c r="D214" s="5" t="s">
         <v>852</v>
       </c>
-      <c r="E214" s="7">
-        <v>1</v>
-      </c>
-      <c r="F214" s="8"/>
-      <c r="G214" s="8"/>
+      <c r="E214" s="8">
+        <v>1</v>
+      </c>
+      <c r="F214" s="4"/>
+      <c r="G214" s="4"/>
     </row>
     <row r="215" ht="152.75" spans="1:7">
       <c r="A215" s="4" t="s">
@@ -8732,14 +8732,14 @@
       <c r="C215" s="4" t="s">
         <v>855</v>
       </c>
-      <c r="D215" s="4" t="s">
+      <c r="D215" s="5" t="s">
         <v>856</v>
       </c>
-      <c r="E215" s="7">
-        <v>1</v>
-      </c>
-      <c r="F215" s="8"/>
-      <c r="G215" s="8"/>
+      <c r="E215" s="8">
+        <v>1</v>
+      </c>
+      <c r="F215" s="4"/>
+      <c r="G215" s="4"/>
     </row>
     <row r="216" ht="107.75" spans="1:7">
       <c r="A216" s="4" t="s">
@@ -8751,14 +8751,14 @@
       <c r="C216" s="4" t="s">
         <v>859</v>
       </c>
-      <c r="D216" s="4" t="s">
+      <c r="D216" s="5" t="s">
         <v>860</v>
       </c>
-      <c r="E216" s="7">
-        <v>1</v>
-      </c>
-      <c r="F216" s="8"/>
-      <c r="G216" s="8"/>
+      <c r="E216" s="8">
+        <v>1</v>
+      </c>
+      <c r="F216" s="4"/>
+      <c r="G216" s="4"/>
     </row>
     <row r="217" ht="92.75" spans="1:7">
       <c r="A217" s="4" t="s">
@@ -8770,14 +8770,14 @@
       <c r="C217" s="4" t="s">
         <v>863</v>
       </c>
-      <c r="D217" s="4" t="s">
+      <c r="D217" s="5" t="s">
         <v>864</v>
       </c>
-      <c r="E217" s="7">
-        <v>1</v>
-      </c>
-      <c r="F217" s="8"/>
-      <c r="G217" s="8"/>
+      <c r="E217" s="8">
+        <v>1</v>
+      </c>
+      <c r="F217" s="4"/>
+      <c r="G217" s="4"/>
     </row>
     <row r="218" ht="289.75" spans="1:7">
       <c r="A218" s="4" t="s">
@@ -8789,14 +8789,14 @@
       <c r="C218" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="D218" s="4" t="s">
+      <c r="D218" s="5" t="s">
         <v>868</v>
       </c>
-      <c r="E218" s="7">
-        <v>1</v>
-      </c>
-      <c r="F218" s="8"/>
-      <c r="G218" s="8"/>
+      <c r="E218" s="8">
+        <v>1</v>
+      </c>
+      <c r="F218" s="4"/>
+      <c r="G218" s="4"/>
     </row>
     <row r="219" ht="152.75" spans="1:7">
       <c r="A219" s="4" t="s">
@@ -8808,14 +8808,14 @@
       <c r="C219" s="4" t="s">
         <v>871</v>
       </c>
-      <c r="D219" s="4" t="s">
+      <c r="D219" s="5" t="s">
         <v>872</v>
       </c>
-      <c r="E219" s="7">
-        <v>1</v>
-      </c>
-      <c r="F219" s="8"/>
-      <c r="G219" s="8"/>
+      <c r="E219" s="8">
+        <v>1</v>
+      </c>
+      <c r="F219" s="4"/>
+      <c r="G219" s="4"/>
     </row>
     <row r="220" ht="137.75" spans="1:7">
       <c r="A220" s="4" t="s">
@@ -8827,14 +8827,14 @@
       <c r="C220" s="4" t="s">
         <v>875</v>
       </c>
-      <c r="D220" s="4" t="s">
+      <c r="D220" s="5" t="s">
         <v>876</v>
       </c>
-      <c r="E220" s="7">
-        <v>1</v>
-      </c>
-      <c r="F220" s="8"/>
-      <c r="G220" s="8"/>
+      <c r="E220" s="8">
+        <v>1</v>
+      </c>
+      <c r="F220" s="4"/>
+      <c r="G220" s="4"/>
     </row>
     <row r="221" ht="259.75" spans="1:7">
       <c r="A221" s="4" t="s">
@@ -8846,14 +8846,14 @@
       <c r="C221" s="4" t="s">
         <v>879</v>
       </c>
-      <c r="D221" s="4" t="s">
+      <c r="D221" s="5" t="s">
         <v>880</v>
       </c>
-      <c r="E221" s="7">
-        <v>1</v>
-      </c>
-      <c r="F221" s="8"/>
-      <c r="G221" s="8"/>
+      <c r="E221" s="8">
+        <v>1</v>
+      </c>
+      <c r="F221" s="4"/>
+      <c r="G221" s="4"/>
     </row>
     <row r="222" ht="274.75" spans="1:7">
       <c r="A222" s="4" t="s">
@@ -8865,14 +8865,14 @@
       <c r="C222" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="D222" s="4" t="s">
+      <c r="D222" s="5" t="s">
         <v>884</v>
       </c>
-      <c r="E222" s="7">
-        <v>1</v>
-      </c>
-      <c r="F222" s="8"/>
-      <c r="G222" s="8"/>
+      <c r="E222" s="8">
+        <v>1</v>
+      </c>
+      <c r="F222" s="4"/>
+      <c r="G222" s="4"/>
     </row>
     <row r="223" ht="107.75" spans="1:7">
       <c r="A223" s="4" t="s">
@@ -8884,14 +8884,14 @@
       <c r="C223" s="4" t="s">
         <v>887</v>
       </c>
-      <c r="D223" s="4" t="s">
+      <c r="D223" s="5" t="s">
         <v>888</v>
       </c>
-      <c r="E223" s="7">
-        <v>1</v>
-      </c>
-      <c r="F223" s="8"/>
-      <c r="G223" s="8"/>
+      <c r="E223" s="8">
+        <v>1</v>
+      </c>
+      <c r="F223" s="4"/>
+      <c r="G223" s="4"/>
     </row>
     <row r="224" ht="107.75" spans="1:7">
       <c r="A224" s="4" t="s">
@@ -8903,14 +8903,14 @@
       <c r="C224" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="D224" s="4" t="s">
+      <c r="D224" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="E224" s="7">
-        <v>1</v>
-      </c>
-      <c r="F224" s="8"/>
-      <c r="G224" s="8"/>
+      <c r="E224" s="8">
+        <v>1</v>
+      </c>
+      <c r="F224" s="4"/>
+      <c r="G224" s="4"/>
     </row>
     <row r="225" ht="92.75" spans="1:7">
       <c r="A225" s="4" t="s">
@@ -8922,14 +8922,14 @@
       <c r="C225" s="4" t="s">
         <v>895</v>
       </c>
-      <c r="D225" s="4" t="s">
+      <c r="D225" s="5" t="s">
         <v>896</v>
       </c>
-      <c r="E225" s="7">
-        <v>1</v>
-      </c>
-      <c r="F225" s="8"/>
-      <c r="G225" s="8"/>
+      <c r="E225" s="8">
+        <v>1</v>
+      </c>
+      <c r="F225" s="4"/>
+      <c r="G225" s="4"/>
     </row>
     <row r="226" ht="198.75" spans="1:7">
       <c r="A226" s="4" t="s">
@@ -8941,14 +8941,14 @@
       <c r="C226" s="4" t="s">
         <v>899</v>
       </c>
-      <c r="D226" s="4" t="s">
+      <c r="D226" s="5" t="s">
         <v>900</v>
       </c>
-      <c r="E226" s="7">
-        <v>1</v>
-      </c>
-      <c r="F226" s="8"/>
-      <c r="G226" s="8"/>
+      <c r="E226" s="8">
+        <v>1</v>
+      </c>
+      <c r="F226" s="4"/>
+      <c r="G226" s="4"/>
     </row>
     <row r="227" ht="137.75" spans="1:7">
       <c r="A227" s="4" t="s">
@@ -8960,14 +8960,14 @@
       <c r="C227" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="D227" s="4" t="s">
+      <c r="D227" s="5" t="s">
         <v>904</v>
       </c>
-      <c r="E227" s="7">
-        <v>1</v>
-      </c>
-      <c r="F227" s="8"/>
-      <c r="G227" s="8"/>
+      <c r="E227" s="8">
+        <v>1</v>
+      </c>
+      <c r="F227" s="4"/>
+      <c r="G227" s="4"/>
     </row>
     <row r="228" ht="92.75" spans="1:7">
       <c r="A228" s="4" t="s">
@@ -8979,14 +8979,14 @@
       <c r="C228" s="4" t="s">
         <v>907</v>
       </c>
-      <c r="D228" s="4" t="s">
+      <c r="D228" s="5" t="s">
         <v>908</v>
       </c>
-      <c r="E228" s="7">
-        <v>1</v>
-      </c>
-      <c r="F228" s="8"/>
-      <c r="G228" s="8"/>
+      <c r="E228" s="8">
+        <v>1</v>
+      </c>
+      <c r="F228" s="4"/>
+      <c r="G228" s="4"/>
     </row>
     <row r="229" ht="107.75" spans="1:7">
       <c r="A229" s="4" t="s">
@@ -8998,14 +8998,14 @@
       <c r="C229" s="4" t="s">
         <v>910</v>
       </c>
-      <c r="D229" s="4" t="s">
+      <c r="D229" s="5" t="s">
         <v>911</v>
       </c>
-      <c r="E229" s="7">
+      <c r="E229" s="8">
         <v>0</v>
       </c>
-      <c r="F229" s="8"/>
-      <c r="G229" s="8"/>
+      <c r="F229" s="4"/>
+      <c r="G229" s="4"/>
     </row>
     <row r="230" ht="228.75" spans="1:7">
       <c r="A230" s="4" t="s">
@@ -9017,14 +9017,14 @@
       <c r="C230" s="4" t="s">
         <v>914</v>
       </c>
-      <c r="D230" s="4" t="s">
+      <c r="D230" s="5" t="s">
         <v>915</v>
       </c>
-      <c r="E230" s="7">
+      <c r="E230" s="8">
         <v>0</v>
       </c>
-      <c r="F230" s="8"/>
-      <c r="G230" s="8"/>
+      <c r="F230" s="4"/>
+      <c r="G230" s="4"/>
     </row>
     <row r="231" ht="122.75" spans="1:7">
       <c r="A231" s="4" t="s">
@@ -9036,14 +9036,14 @@
       <c r="C231" s="4" t="s">
         <v>918</v>
       </c>
-      <c r="D231" s="4" t="s">
+      <c r="D231" s="5" t="s">
         <v>919</v>
       </c>
-      <c r="E231" s="7">
+      <c r="E231" s="8">
         <v>0</v>
       </c>
-      <c r="F231" s="8"/>
-      <c r="G231" s="8"/>
+      <c r="F231" s="4"/>
+      <c r="G231" s="4"/>
     </row>
     <row r="232" ht="107.75" spans="1:7">
       <c r="A232" s="4" t="s">
@@ -9055,14 +9055,14 @@
       <c r="C232" s="4" t="s">
         <v>922</v>
       </c>
-      <c r="D232" s="4" t="s">
+      <c r="D232" s="5" t="s">
         <v>923</v>
       </c>
-      <c r="E232" s="7">
+      <c r="E232" s="8">
         <v>0</v>
       </c>
-      <c r="F232" s="8"/>
-      <c r="G232" s="8"/>
+      <c r="F232" s="4"/>
+      <c r="G232" s="4"/>
     </row>
     <row r="233" ht="76.75" spans="1:7">
       <c r="A233" s="4" t="s">
@@ -9074,14 +9074,14 @@
       <c r="C233" s="4" t="s">
         <v>925</v>
       </c>
-      <c r="D233" s="4" t="s">
+      <c r="D233" s="5" t="s">
         <v>926</v>
       </c>
-      <c r="E233" s="7">
+      <c r="E233" s="8">
         <v>0</v>
       </c>
-      <c r="F233" s="8"/>
-      <c r="G233" s="8"/>
+      <c r="F233" s="4"/>
+      <c r="G233" s="4"/>
     </row>
     <row r="234" ht="122.75" spans="1:7">
       <c r="A234" s="4" t="s">
@@ -9093,16 +9093,16 @@
       <c r="C234" s="4" t="s">
         <v>929</v>
       </c>
-      <c r="D234" s="4" t="s">
+      <c r="D234" s="5" t="s">
         <v>930</v>
       </c>
-      <c r="E234" s="7">
+      <c r="E234" s="8">
         <v>0</v>
       </c>
-      <c r="F234" s="8"/>
-      <c r="G234" s="8"/>
-    </row>
-    <row r="235" ht="122.75" spans="1:7">
+      <c r="F234" s="4"/>
+      <c r="G234" s="4"/>
+    </row>
+    <row r="235" ht="152.75" spans="1:7">
       <c r="A235" s="4" t="s">
         <v>931</v>
       </c>
@@ -9112,14 +9112,14 @@
       <c r="C235" s="4" t="s">
         <v>933</v>
       </c>
-      <c r="D235" s="4" t="s">
+      <c r="D235" s="5" t="s">
         <v>934</v>
       </c>
-      <c r="E235" s="7">
+      <c r="E235" s="8">
         <v>0</v>
       </c>
-      <c r="F235" s="8"/>
-      <c r="G235" s="8"/>
+      <c r="F235" s="4"/>
+      <c r="G235" s="4"/>
     </row>
     <row r="236" ht="92.75" spans="1:7">
       <c r="A236" s="4" t="s">
@@ -9131,16 +9131,16 @@
       <c r="C236" s="4" t="s">
         <v>937</v>
       </c>
-      <c r="D236" s="4" t="s">
+      <c r="D236" s="5" t="s">
         <v>938</v>
       </c>
-      <c r="E236" s="7">
+      <c r="E236" s="8">
         <v>0</v>
       </c>
-      <c r="F236" s="8"/>
-      <c r="G236" s="8"/>
-    </row>
-    <row r="237" ht="107.75" spans="1:7">
+      <c r="F236" s="4"/>
+      <c r="G236" s="4"/>
+    </row>
+    <row r="237" ht="228.75" spans="1:7">
       <c r="A237" s="4" t="s">
         <v>939</v>
       </c>
@@ -9150,14 +9150,14 @@
       <c r="C237" s="4" t="s">
         <v>941</v>
       </c>
-      <c r="D237" s="4" t="s">
+      <c r="D237" s="5" t="s">
         <v>942</v>
       </c>
-      <c r="E237" s="7">
+      <c r="E237" s="8">
         <v>0</v>
       </c>
-      <c r="F237" s="8"/>
-      <c r="G237" s="8"/>
+      <c r="F237" s="4"/>
+      <c r="G237" s="4"/>
     </row>
     <row r="238" ht="228.75" spans="1:7">
       <c r="A238" s="4" t="s">
@@ -9169,14 +9169,14 @@
       <c r="C238" s="4" t="s">
         <v>945</v>
       </c>
-      <c r="D238" s="4" t="s">
+      <c r="D238" s="5" t="s">
         <v>946</v>
       </c>
-      <c r="E238" s="7">
+      <c r="E238" s="8">
         <v>0</v>
       </c>
-      <c r="F238" s="8"/>
-      <c r="G238" s="8"/>
+      <c r="F238" s="4"/>
+      <c r="G238" s="4"/>
     </row>
     <row r="239" ht="198.75" spans="1:7">
       <c r="A239" s="4" t="s">
@@ -9188,33 +9188,33 @@
       <c r="C239" s="4" t="s">
         <v>949</v>
       </c>
-      <c r="D239" s="4" t="s">
+      <c r="D239" s="5" t="s">
         <v>950</v>
       </c>
-      <c r="E239" s="7">
+      <c r="E239" s="8">
         <v>0</v>
       </c>
-      <c r="F239" s="8"/>
-      <c r="G239" s="8"/>
+      <c r="F239" s="4"/>
+      <c r="G239" s="4"/>
     </row>
     <row r="240" ht="183.75" spans="1:7">
       <c r="A240" s="4" t="s">
         <v>951</v>
       </c>
-      <c r="B240" s="5" t="s">
+      <c r="B240" s="6" t="s">
         <v>438</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>952</v>
       </c>
-      <c r="D240" s="4" t="s">
+      <c r="D240" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="E240" s="7">
+      <c r="E240" s="8">
         <v>0</v>
       </c>
-      <c r="F240" s="8"/>
-      <c r="G240" s="8"/>
+      <c r="F240" s="4"/>
+      <c r="G240" s="4"/>
     </row>
     <row r="241" ht="244.75" spans="1:7">
       <c r="A241" s="4" t="s">
@@ -9226,14 +9226,14 @@
       <c r="C241" s="4" t="s">
         <v>956</v>
       </c>
-      <c r="D241" s="4" t="s">
+      <c r="D241" s="5" t="s">
         <v>957</v>
       </c>
-      <c r="E241" s="7">
+      <c r="E241" s="8">
         <v>0</v>
       </c>
-      <c r="F241" s="8"/>
-      <c r="G241" s="8"/>
+      <c r="F241" s="4"/>
+      <c r="G241" s="4"/>
     </row>
     <row r="242" ht="107.75" spans="1:7">
       <c r="A242" s="4" t="s">
@@ -9245,14 +9245,14 @@
       <c r="C242" s="4" t="s">
         <v>960</v>
       </c>
-      <c r="D242" s="4" t="s">
+      <c r="D242" s="5" t="s">
         <v>961</v>
       </c>
-      <c r="E242" s="7">
+      <c r="E242" s="8">
         <v>0</v>
       </c>
-      <c r="F242" s="8"/>
-      <c r="G242" s="8"/>
+      <c r="F242" s="4"/>
+      <c r="G242" s="4"/>
     </row>
     <row r="243" ht="76.75" spans="1:7">
       <c r="A243" s="4" t="s">
@@ -9264,14 +9264,14 @@
       <c r="C243" s="4" t="s">
         <v>964</v>
       </c>
-      <c r="D243" s="4" t="s">
+      <c r="D243" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="E243" s="7">
+      <c r="E243" s="8">
         <v>0</v>
       </c>
-      <c r="F243" s="8"/>
-      <c r="G243" s="8"/>
+      <c r="F243" s="4"/>
+      <c r="G243" s="4"/>
     </row>
     <row r="244" ht="76.75" spans="1:7">
       <c r="A244" s="4" t="s">
@@ -9283,14 +9283,14 @@
       <c r="C244" s="4" t="s">
         <v>968</v>
       </c>
-      <c r="D244" s="4" t="s">
+      <c r="D244" s="5" t="s">
         <v>969</v>
       </c>
-      <c r="E244" s="7">
+      <c r="E244" s="8">
         <v>0</v>
       </c>
-      <c r="F244" s="8"/>
-      <c r="G244" s="8"/>
+      <c r="F244" s="4"/>
+      <c r="G244" s="4"/>
     </row>
     <row r="245" ht="92.75" spans="1:7">
       <c r="A245" s="4" t="s">
@@ -9302,14 +9302,14 @@
       <c r="C245" s="4" t="s">
         <v>972</v>
       </c>
-      <c r="D245" s="4" t="s">
+      <c r="D245" s="5" t="s">
         <v>973</v>
       </c>
-      <c r="E245" s="7">
+      <c r="E245" s="8">
         <v>0</v>
       </c>
-      <c r="F245" s="8"/>
-      <c r="G245" s="8"/>
+      <c r="F245" s="4"/>
+      <c r="G245" s="4"/>
     </row>
     <row r="246" ht="137.75" spans="1:7">
       <c r="A246" s="4" t="s">
@@ -9321,14 +9321,14 @@
       <c r="C246" s="4" t="s">
         <v>976</v>
       </c>
-      <c r="D246" s="4" t="s">
+      <c r="D246" s="5" t="s">
         <v>977</v>
       </c>
-      <c r="E246" s="7">
+      <c r="E246" s="8">
         <v>0</v>
       </c>
-      <c r="F246" s="8"/>
-      <c r="G246" s="8"/>
+      <c r="F246" s="4"/>
+      <c r="G246" s="4"/>
     </row>
     <row r="247" ht="76.75" spans="1:7">
       <c r="A247" s="4" t="s">
@@ -9340,14 +9340,14 @@
       <c r="C247" s="4" t="s">
         <v>980</v>
       </c>
-      <c r="D247" s="4" t="s">
+      <c r="D247" s="5" t="s">
         <v>981</v>
       </c>
-      <c r="E247" s="7">
+      <c r="E247" s="8">
         <v>0</v>
       </c>
-      <c r="F247" s="8"/>
-      <c r="G247" s="8"/>
+      <c r="F247" s="4"/>
+      <c r="G247" s="4"/>
     </row>
     <row r="248" ht="213.75" spans="1:7">
       <c r="A248" s="4" t="s">
@@ -9359,14 +9359,14 @@
       <c r="C248" s="4" t="s">
         <v>983</v>
       </c>
-      <c r="D248" s="4" t="s">
+      <c r="D248" s="5" t="s">
         <v>984</v>
       </c>
-      <c r="E248" s="7">
+      <c r="E248" s="8">
         <v>0</v>
       </c>
-      <c r="F248" s="8"/>
-      <c r="G248" s="8"/>
+      <c r="F248" s="4"/>
+      <c r="G248" s="4"/>
     </row>
     <row r="249" ht="92.75" spans="1:7">
       <c r="A249" s="4" t="s">
@@ -9378,14 +9378,14 @@
       <c r="C249" s="4" t="s">
         <v>987</v>
       </c>
-      <c r="D249" s="4" t="s">
+      <c r="D249" s="5" t="s">
         <v>988</v>
       </c>
-      <c r="E249" s="7">
+      <c r="E249" s="8">
         <v>0</v>
       </c>
-      <c r="F249" s="8"/>
-      <c r="G249" s="8"/>
+      <c r="F249" s="4"/>
+      <c r="G249" s="4"/>
     </row>
     <row r="250" ht="122.75" spans="1:7">
       <c r="A250" s="4" t="s">
@@ -9397,14 +9397,14 @@
       <c r="C250" s="4" t="s">
         <v>991</v>
       </c>
-      <c r="D250" s="4" t="s">
+      <c r="D250" s="5" t="s">
         <v>992</v>
       </c>
-      <c r="E250" s="7">
+      <c r="E250" s="8">
         <v>0</v>
       </c>
-      <c r="F250" s="8"/>
-      <c r="G250" s="8"/>
+      <c r="F250" s="4"/>
+      <c r="G250" s="4"/>
     </row>
     <row r="251" ht="107.75" spans="1:7">
       <c r="A251" s="4" t="s">
@@ -9416,14 +9416,14 @@
       <c r="C251" s="4" t="s">
         <v>995</v>
       </c>
-      <c r="D251" s="4" t="s">
+      <c r="D251" s="5" t="s">
         <v>996</v>
       </c>
-      <c r="E251" s="7">
+      <c r="E251" s="8">
         <v>0</v>
       </c>
-      <c r="F251" s="8"/>
-      <c r="G251" s="8"/>
+      <c r="F251" s="4"/>
+      <c r="G251" s="4"/>
     </row>
     <row r="252" ht="92.75" spans="1:7">
       <c r="A252" s="4" t="s">
@@ -9435,14 +9435,14 @@
       <c r="C252" s="4" t="s">
         <v>999</v>
       </c>
-      <c r="D252" s="4" t="s">
+      <c r="D252" s="5" t="s">
         <v>1000</v>
       </c>
-      <c r="E252" s="7">
+      <c r="E252" s="8">
         <v>0</v>
       </c>
-      <c r="F252" s="8"/>
-      <c r="G252" s="8"/>
+      <c r="F252" s="4"/>
+      <c r="G252" s="4"/>
     </row>
     <row r="253" ht="76.75" spans="1:7">
       <c r="A253" s="4" t="s">
@@ -9454,14 +9454,14 @@
       <c r="C253" s="4" t="s">
         <v>1003</v>
       </c>
-      <c r="D253" s="4" t="s">
+      <c r="D253" s="5" t="s">
         <v>1004</v>
       </c>
-      <c r="E253" s="7">
+      <c r="E253" s="8">
         <v>0</v>
       </c>
-      <c r="F253" s="8"/>
-      <c r="G253" s="8"/>
+      <c r="F253" s="4"/>
+      <c r="G253" s="4"/>
     </row>
     <row r="254" ht="228.75" spans="1:7">
       <c r="A254" s="4" t="s">
@@ -9473,14 +9473,14 @@
       <c r="C254" s="4" t="s">
         <v>1007</v>
       </c>
-      <c r="D254" s="4" t="s">
+      <c r="D254" s="5" t="s">
         <v>1008</v>
       </c>
-      <c r="E254" s="7">
+      <c r="E254" s="8">
         <v>0</v>
       </c>
-      <c r="F254" s="8"/>
-      <c r="G254" s="8"/>
+      <c r="F254" s="4"/>
+      <c r="G254" s="4"/>
     </row>
     <row r="255" ht="107.75" spans="1:7">
       <c r="A255" s="4" t="s">
@@ -9492,14 +9492,14 @@
       <c r="C255" s="4" t="s">
         <v>1011</v>
       </c>
-      <c r="D255" s="4" t="s">
+      <c r="D255" s="5" t="s">
         <v>1012</v>
       </c>
-      <c r="E255" s="7">
+      <c r="E255" s="8">
         <v>0</v>
       </c>
-      <c r="F255" s="8"/>
-      <c r="G255" s="8"/>
+      <c r="F255" s="4"/>
+      <c r="G255" s="4"/>
     </row>
     <row r="256" ht="198.75" spans="1:7">
       <c r="A256" s="4" t="s">
@@ -9511,14 +9511,14 @@
       <c r="C256" s="4" t="s">
         <v>1015</v>
       </c>
-      <c r="D256" s="4" t="s">
+      <c r="D256" s="5" t="s">
         <v>1016</v>
       </c>
-      <c r="E256" s="7">
+      <c r="E256" s="8">
         <v>0</v>
       </c>
-      <c r="F256" s="8"/>
-      <c r="G256" s="8"/>
+      <c r="F256" s="4"/>
+      <c r="G256" s="4"/>
     </row>
     <row r="257" ht="92.75" spans="1:7">
       <c r="A257" s="4" t="s">
@@ -9530,14 +9530,14 @@
       <c r="C257" s="4" t="s">
         <v>1018</v>
       </c>
-      <c r="D257" s="4" t="s">
+      <c r="D257" s="5" t="s">
         <v>1019</v>
       </c>
-      <c r="E257" s="7">
+      <c r="E257" s="8">
         <v>0</v>
       </c>
-      <c r="F257" s="8"/>
-      <c r="G257" s="8"/>
+      <c r="F257" s="4"/>
+      <c r="G257" s="4"/>
     </row>
     <row r="258" ht="92.75" spans="1:7">
       <c r="A258" s="4" t="s">
@@ -9549,14 +9549,14 @@
       <c r="C258" s="4" t="s">
         <v>1022</v>
       </c>
-      <c r="D258" s="4" t="s">
+      <c r="D258" s="5" t="s">
         <v>1023</v>
       </c>
-      <c r="E258" s="7">
+      <c r="E258" s="8">
         <v>0</v>
       </c>
-      <c r="F258" s="8"/>
-      <c r="G258" s="8"/>
+      <c r="F258" s="4"/>
+      <c r="G258" s="4"/>
     </row>
     <row r="259" ht="107.75" spans="1:7">
       <c r="A259" s="4" t="s">
@@ -9568,14 +9568,14 @@
       <c r="C259" s="4" t="s">
         <v>1025</v>
       </c>
-      <c r="D259" s="4" t="s">
+      <c r="D259" s="5" t="s">
         <v>1026</v>
       </c>
-      <c r="E259" s="7">
+      <c r="E259" s="8">
         <v>0</v>
       </c>
-      <c r="F259" s="8"/>
-      <c r="G259" s="8"/>
+      <c r="F259" s="4"/>
+      <c r="G259" s="4"/>
     </row>
     <row r="260" ht="92.75" spans="1:7">
       <c r="A260" s="4" t="s">
@@ -9587,14 +9587,14 @@
       <c r="C260" s="4" t="s">
         <v>1028</v>
       </c>
-      <c r="D260" s="4" t="s">
+      <c r="D260" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="E260" s="7">
+      <c r="E260" s="8">
         <v>0</v>
       </c>
-      <c r="F260" s="8"/>
-      <c r="G260" s="8"/>
+      <c r="F260" s="4"/>
+      <c r="G260" s="4"/>
     </row>
     <row r="261" ht="122.75" spans="1:7">
       <c r="A261" s="4" t="s">
@@ -9606,14 +9606,14 @@
       <c r="C261" s="4" t="s">
         <v>1031</v>
       </c>
-      <c r="D261" s="4" t="s">
+      <c r="D261" s="5" t="s">
         <v>1032</v>
       </c>
-      <c r="E261" s="7">
+      <c r="E261" s="8">
         <v>0</v>
       </c>
-      <c r="F261" s="8"/>
-      <c r="G261" s="8"/>
+      <c r="F261" s="4"/>
+      <c r="G261" s="4"/>
     </row>
     <row r="262" ht="107.75" spans="1:7">
       <c r="A262" s="4" t="s">
@@ -9625,14 +9625,14 @@
       <c r="C262" s="4" t="s">
         <v>1034</v>
       </c>
-      <c r="D262" s="4" t="s">
+      <c r="D262" s="5" t="s">
         <v>1035</v>
       </c>
-      <c r="E262" s="7">
+      <c r="E262" s="8">
         <v>0</v>
       </c>
-      <c r="F262" s="8"/>
-      <c r="G262" s="8"/>
+      <c r="F262" s="4"/>
+      <c r="G262" s="4"/>
     </row>
     <row r="263" ht="259.75" spans="1:7">
       <c r="A263" s="4" t="s">
@@ -9644,14 +9644,14 @@
       <c r="C263" s="4" t="s">
         <v>1038</v>
       </c>
-      <c r="D263" s="4" t="s">
+      <c r="D263" s="5" t="s">
         <v>1039</v>
       </c>
-      <c r="E263" s="7">
+      <c r="E263" s="8">
         <v>0</v>
       </c>
-      <c r="F263" s="8"/>
-      <c r="G263" s="8"/>
+      <c r="F263" s="4"/>
+      <c r="G263" s="4"/>
     </row>
     <row r="264" ht="228.75" spans="1:7">
       <c r="A264" s="4" t="s">
@@ -9663,14 +9663,14 @@
       <c r="C264" s="4" t="s">
         <v>1042</v>
       </c>
-      <c r="D264" s="4" t="s">
+      <c r="D264" s="5" t="s">
         <v>1043</v>
       </c>
-      <c r="E264" s="7">
+      <c r="E264" s="8">
         <v>0</v>
       </c>
-      <c r="F264" s="8"/>
-      <c r="G264" s="8"/>
+      <c r="F264" s="4"/>
+      <c r="G264" s="4"/>
     </row>
     <row r="265" ht="92.75" spans="1:7">
       <c r="A265" s="4" t="s">
@@ -9682,14 +9682,14 @@
       <c r="C265" s="4" t="s">
         <v>1045</v>
       </c>
-      <c r="D265" s="4" t="s">
+      <c r="D265" s="5" t="s">
         <v>1046</v>
       </c>
-      <c r="E265" s="7">
+      <c r="E265" s="8">
         <v>0</v>
       </c>
-      <c r="F265" s="8"/>
-      <c r="G265" s="8"/>
+      <c r="F265" s="4"/>
+      <c r="G265" s="4"/>
     </row>
     <row r="266" ht="107.75" spans="1:7">
       <c r="A266" s="4" t="s">
@@ -9701,14 +9701,14 @@
       <c r="C266" s="4" t="s">
         <v>1048</v>
       </c>
-      <c r="D266" s="4" t="s">
+      <c r="D266" s="5" t="s">
         <v>1049</v>
       </c>
-      <c r="E266" s="7">
+      <c r="E266" s="8">
         <v>0</v>
       </c>
-      <c r="F266" s="8"/>
-      <c r="G266" s="8"/>
+      <c r="F266" s="4"/>
+      <c r="G266" s="4"/>
     </row>
     <row r="267" ht="244.75" spans="1:7">
       <c r="A267" s="4" t="s">
@@ -9720,14 +9720,14 @@
       <c r="C267" s="4" t="s">
         <v>1052</v>
       </c>
-      <c r="D267" s="4" t="s">
+      <c r="D267" s="5" t="s">
         <v>1053</v>
       </c>
-      <c r="E267" s="7">
+      <c r="E267" s="8">
         <v>0</v>
       </c>
-      <c r="F267" s="8"/>
-      <c r="G267" s="8"/>
+      <c r="F267" s="4"/>
+      <c r="G267" s="4"/>
     </row>
     <row r="268" ht="183.75" spans="1:7">
       <c r="A268" s="4" t="s">
@@ -9739,14 +9739,14 @@
       <c r="C268" s="4" t="s">
         <v>1056</v>
       </c>
-      <c r="D268" s="4" t="s">
+      <c r="D268" s="5" t="s">
         <v>1057</v>
       </c>
-      <c r="E268" s="7">
+      <c r="E268" s="8">
         <v>0</v>
       </c>
-      <c r="F268" s="8"/>
-      <c r="G268" s="8"/>
+      <c r="F268" s="4"/>
+      <c r="G268" s="4"/>
     </row>
     <row r="269" ht="304.75" spans="1:7">
       <c r="A269" s="4" t="s">
@@ -9758,14 +9758,14 @@
       <c r="C269" s="4" t="s">
         <v>1060</v>
       </c>
-      <c r="D269" s="4" t="s">
+      <c r="D269" s="5" t="s">
         <v>1061</v>
       </c>
-      <c r="E269" s="7">
+      <c r="E269" s="8">
         <v>0</v>
       </c>
-      <c r="F269" s="8"/>
-      <c r="G269" s="8"/>
+      <c r="F269" s="4"/>
+      <c r="G269" s="4"/>
     </row>
     <row r="270" ht="289.75" spans="1:7">
       <c r="A270" s="4" t="s">
@@ -9777,14 +9777,14 @@
       <c r="C270" s="4" t="s">
         <v>1064</v>
       </c>
-      <c r="D270" s="4" t="s">
+      <c r="D270" s="5" t="s">
         <v>1065</v>
       </c>
-      <c r="E270" s="7">
+      <c r="E270" s="8">
         <v>0</v>
       </c>
-      <c r="F270" s="8"/>
-      <c r="G270" s="8"/>
+      <c r="F270" s="4"/>
+      <c r="G270" s="4"/>
     </row>
     <row r="271" ht="244.75" spans="1:7">
       <c r="A271" s="4" t="s">
@@ -9796,14 +9796,14 @@
       <c r="C271" s="4" t="s">
         <v>1068</v>
       </c>
-      <c r="D271" s="4" t="s">
+      <c r="D271" s="5" t="s">
         <v>1069</v>
       </c>
-      <c r="E271" s="7">
+      <c r="E271" s="8">
         <v>0</v>
       </c>
-      <c r="F271" s="8"/>
-      <c r="G271" s="8"/>
+      <c r="F271" s="4"/>
+      <c r="G271" s="4"/>
     </row>
     <row r="272" ht="168.75" spans="1:7">
       <c r="A272" s="4" t="s">
@@ -9815,14 +9815,14 @@
       <c r="C272" s="4" t="s">
         <v>1071</v>
       </c>
-      <c r="D272" s="4" t="s">
+      <c r="D272" s="5" t="s">
         <v>1072</v>
       </c>
-      <c r="E272" s="7">
+      <c r="E272" s="8">
         <v>0</v>
       </c>
-      <c r="F272" s="8"/>
-      <c r="G272" s="8"/>
+      <c r="F272" s="4"/>
+      <c r="G272" s="4"/>
     </row>
     <row r="273" ht="122.75" spans="1:7">
       <c r="A273" s="4" t="s">
@@ -9834,14 +9834,14 @@
       <c r="C273" s="4" t="s">
         <v>1074</v>
       </c>
-      <c r="D273" s="4" t="s">
+      <c r="D273" s="5" t="s">
         <v>1075</v>
       </c>
-      <c r="E273" s="7">
+      <c r="E273" s="8">
         <v>0</v>
       </c>
-      <c r="F273" s="8"/>
-      <c r="G273" s="8"/>
+      <c r="F273" s="4"/>
+      <c r="G273" s="4"/>
     </row>
     <row r="274" ht="92.75" spans="1:7">
       <c r="A274" s="4" t="s">
@@ -9853,14 +9853,14 @@
       <c r="C274" s="4" t="s">
         <v>1078</v>
       </c>
-      <c r="D274" s="4" t="s">
+      <c r="D274" s="5" t="s">
         <v>1079</v>
       </c>
-      <c r="E274" s="7">
+      <c r="E274" s="8">
         <v>0</v>
       </c>
-      <c r="F274" s="8"/>
-      <c r="G274" s="8"/>
+      <c r="F274" s="4"/>
+      <c r="G274" s="4"/>
     </row>
     <row r="275" ht="198.75" spans="1:7">
       <c r="A275" s="4" t="s">
@@ -9872,14 +9872,14 @@
       <c r="C275" s="4" t="s">
         <v>1081</v>
       </c>
-      <c r="D275" s="4" t="s">
+      <c r="D275" s="5" t="s">
         <v>1082</v>
       </c>
-      <c r="E275" s="7">
+      <c r="E275" s="8">
         <v>0</v>
       </c>
-      <c r="F275" s="8"/>
-      <c r="G275" s="8"/>
+      <c r="F275" s="4"/>
+      <c r="G275" s="4"/>
     </row>
     <row r="276" ht="107.75" spans="1:7">
       <c r="A276" s="4" t="s">
@@ -9891,14 +9891,14 @@
       <c r="C276" s="4" t="s">
         <v>1084</v>
       </c>
-      <c r="D276" s="4" t="s">
+      <c r="D276" s="5" t="s">
         <v>1085</v>
       </c>
-      <c r="E276" s="7">
+      <c r="E276" s="8">
         <v>0</v>
       </c>
-      <c r="F276" s="8"/>
-      <c r="G276" s="8"/>
+      <c r="F276" s="4"/>
+      <c r="G276" s="4"/>
     </row>
     <row r="277" ht="259.75" spans="1:7">
       <c r="A277" s="4" t="s">
@@ -9910,14 +9910,14 @@
       <c r="C277" s="4" t="s">
         <v>1088</v>
       </c>
-      <c r="D277" s="4" t="s">
+      <c r="D277" s="5" t="s">
         <v>1089</v>
       </c>
-      <c r="E277" s="7">
+      <c r="E277" s="8">
         <v>0</v>
       </c>
-      <c r="F277" s="8"/>
-      <c r="G277" s="8"/>
+      <c r="F277" s="4"/>
+      <c r="G277" s="4"/>
     </row>
     <row r="278" ht="107.75" spans="1:7">
       <c r="A278" s="4" t="s">
@@ -9929,14 +9929,14 @@
       <c r="C278" s="4" t="s">
         <v>1092</v>
       </c>
-      <c r="D278" s="4" t="s">
+      <c r="D278" s="5" t="s">
         <v>1093</v>
       </c>
-      <c r="E278" s="7">
+      <c r="E278" s="8">
         <v>0</v>
       </c>
-      <c r="F278" s="8"/>
-      <c r="G278" s="8"/>
+      <c r="F278" s="4"/>
+      <c r="G278" s="4"/>
     </row>
     <row r="279" ht="107.75" spans="1:7">
       <c r="A279" s="4" t="s">
@@ -9948,14 +9948,14 @@
       <c r="C279" s="4" t="s">
         <v>1096</v>
       </c>
-      <c r="D279" s="4" t="s">
+      <c r="D279" s="5" t="s">
         <v>1097</v>
       </c>
-      <c r="E279" s="7">
+      <c r="E279" s="8">
         <v>0</v>
       </c>
-      <c r="F279" s="8"/>
-      <c r="G279" s="8"/>
+      <c r="F279" s="4"/>
+      <c r="G279" s="4"/>
     </row>
     <row r="280" ht="76.75" spans="1:7">
       <c r="A280" s="4" t="s">
@@ -9967,14 +9967,14 @@
       <c r="C280" s="4" t="s">
         <v>1100</v>
       </c>
-      <c r="D280" s="4" t="s">
+      <c r="D280" s="5" t="s">
         <v>1101</v>
       </c>
-      <c r="E280" s="7">
+      <c r="E280" s="8">
         <v>0</v>
       </c>
-      <c r="F280" s="8"/>
-      <c r="G280" s="8"/>
+      <c r="F280" s="4"/>
+      <c r="G280" s="4"/>
     </row>
     <row r="281" ht="259.75" spans="1:7">
       <c r="A281" s="4" t="s">
@@ -9986,14 +9986,14 @@
       <c r="C281" s="4" t="s">
         <v>1104</v>
       </c>
-      <c r="D281" s="4" t="s">
+      <c r="D281" s="5" t="s">
         <v>1105</v>
       </c>
-      <c r="E281" s="7">
+      <c r="E281" s="8">
         <v>0</v>
       </c>
-      <c r="F281" s="8"/>
-      <c r="G281" s="8"/>
+      <c r="F281" s="4"/>
+      <c r="G281" s="4"/>
     </row>
     <row r="282" ht="61.75" spans="1:7">
       <c r="A282" s="4" t="s">
@@ -10005,14 +10005,14 @@
       <c r="C282" s="4" t="s">
         <v>1108</v>
       </c>
-      <c r="D282" s="4" t="s">
+      <c r="D282" s="5" t="s">
         <v>1109</v>
       </c>
-      <c r="E282" s="7">
+      <c r="E282" s="8">
         <v>0</v>
       </c>
-      <c r="F282" s="8"/>
-      <c r="G282" s="8"/>
+      <c r="F282" s="4"/>
+      <c r="G282" s="4"/>
     </row>
     <row r="283" ht="122.75" spans="1:7">
       <c r="A283" s="4" t="s">
@@ -10024,14 +10024,14 @@
       <c r="C283" s="4" t="s">
         <v>1112</v>
       </c>
-      <c r="D283" s="4" t="s">
+      <c r="D283" s="5" t="s">
         <v>1113</v>
       </c>
-      <c r="E283" s="7">
+      <c r="E283" s="8">
         <v>0</v>
       </c>
-      <c r="F283" s="8"/>
-      <c r="G283" s="8"/>
+      <c r="F283" s="4"/>
+      <c r="G283" s="4"/>
     </row>
     <row r="284" ht="122.75" spans="1:7">
       <c r="A284" s="4" t="s">
@@ -10043,14 +10043,14 @@
       <c r="C284" s="4" t="s">
         <v>1115</v>
       </c>
-      <c r="D284" s="4" t="s">
+      <c r="D284" s="5" t="s">
         <v>1116</v>
       </c>
-      <c r="E284" s="7">
+      <c r="E284" s="8">
         <v>0</v>
       </c>
-      <c r="F284" s="8"/>
-      <c r="G284" s="8"/>
+      <c r="F284" s="4"/>
+      <c r="G284" s="4"/>
     </row>
     <row r="285" ht="107.75" spans="1:7">
       <c r="A285" s="4" t="s">
@@ -10062,14 +10062,14 @@
       <c r="C285" s="4" t="s">
         <v>1119</v>
       </c>
-      <c r="D285" s="4" t="s">
+      <c r="D285" s="5" t="s">
         <v>1120</v>
       </c>
-      <c r="E285" s="7">
+      <c r="E285" s="8">
         <v>0</v>
       </c>
-      <c r="F285" s="8"/>
-      <c r="G285" s="8"/>
+      <c r="F285" s="4"/>
+      <c r="G285" s="4"/>
     </row>
     <row r="286" ht="228.75" spans="1:7">
       <c r="A286" s="4" t="s">
@@ -10081,14 +10081,14 @@
       <c r="C286" s="4" t="s">
         <v>1122</v>
       </c>
-      <c r="D286" s="4" t="s">
+      <c r="D286" s="5" t="s">
         <v>1123</v>
       </c>
-      <c r="E286" s="7">
+      <c r="E286" s="8">
         <v>0</v>
       </c>
-      <c r="F286" s="8"/>
-      <c r="G286" s="8"/>
+      <c r="F286" s="4"/>
+      <c r="G286" s="4"/>
     </row>
     <row r="287" ht="122.75" spans="1:7">
       <c r="A287" s="4" t="s">
@@ -10100,14 +10100,14 @@
       <c r="C287" s="4" t="s">
         <v>1126</v>
       </c>
-      <c r="D287" s="4" t="s">
+      <c r="D287" s="5" t="s">
         <v>1127</v>
       </c>
-      <c r="E287" s="7">
+      <c r="E287" s="8">
         <v>0</v>
       </c>
-      <c r="F287" s="8"/>
-      <c r="G287" s="8"/>
+      <c r="F287" s="4"/>
+      <c r="G287" s="4"/>
     </row>
     <row r="288" ht="259.75" spans="1:7">
       <c r="A288" s="4" t="s">
@@ -10119,14 +10119,14 @@
       <c r="C288" s="4" t="s">
         <v>1130</v>
       </c>
-      <c r="D288" s="4" t="s">
+      <c r="D288" s="5" t="s">
         <v>1131</v>
       </c>
-      <c r="E288" s="7">
+      <c r="E288" s="8">
         <v>0</v>
       </c>
-      <c r="F288" s="8"/>
-      <c r="G288" s="8"/>
+      <c r="F288" s="4"/>
+      <c r="G288" s="4"/>
     </row>
     <row r="289" ht="168.75" spans="1:7">
       <c r="A289" s="4" t="s">
@@ -10138,14 +10138,14 @@
       <c r="C289" s="4" t="s">
         <v>1134</v>
       </c>
-      <c r="D289" s="4" t="s">
+      <c r="D289" s="5" t="s">
         <v>1135</v>
       </c>
-      <c r="E289" s="7">
+      <c r="E289" s="8">
         <v>0</v>
       </c>
-      <c r="F289" s="8"/>
-      <c r="G289" s="8"/>
+      <c r="F289" s="4"/>
+      <c r="G289" s="4"/>
     </row>
     <row r="290" ht="137.75" spans="1:7">
       <c r="A290" s="4" t="s">
@@ -10157,14 +10157,14 @@
       <c r="C290" s="4" t="s">
         <v>1137</v>
       </c>
-      <c r="D290" s="4" t="s">
+      <c r="D290" s="5" t="s">
         <v>1138</v>
       </c>
-      <c r="E290" s="7">
+      <c r="E290" s="8">
         <v>0</v>
       </c>
-      <c r="F290" s="8"/>
-      <c r="G290" s="8"/>
+      <c r="F290" s="4"/>
+      <c r="G290" s="4"/>
     </row>
     <row r="291" ht="76.75" spans="1:7">
       <c r="A291" s="4" t="s">
@@ -10176,14 +10176,14 @@
       <c r="C291" s="4" t="s">
         <v>1141</v>
       </c>
-      <c r="D291" s="4" t="s">
+      <c r="D291" s="5" t="s">
         <v>1142</v>
       </c>
-      <c r="E291" s="7">
+      <c r="E291" s="8">
         <v>0</v>
       </c>
-      <c r="F291" s="8"/>
-      <c r="G291" s="8"/>
+      <c r="F291" s="4"/>
+      <c r="G291" s="4"/>
     </row>
     <row r="292" ht="92.75" spans="1:7">
       <c r="A292" s="4" t="s">
@@ -10195,14 +10195,14 @@
       <c r="C292" s="4" t="s">
         <v>1144</v>
       </c>
-      <c r="D292" s="4" t="s">
+      <c r="D292" s="5" t="s">
         <v>1145</v>
       </c>
-      <c r="E292" s="7">
+      <c r="E292" s="8">
         <v>0</v>
       </c>
-      <c r="F292" s="8"/>
-      <c r="G292" s="8"/>
+      <c r="F292" s="4"/>
+      <c r="G292" s="4"/>
     </row>
     <row r="293" ht="137.75" spans="1:7">
       <c r="A293" s="4" t="s">
@@ -10214,14 +10214,14 @@
       <c r="C293" s="4" t="s">
         <v>1148</v>
       </c>
-      <c r="D293" s="4" t="s">
+      <c r="D293" s="5" t="s">
         <v>1149</v>
       </c>
-      <c r="E293" s="7">
+      <c r="E293" s="8">
         <v>0</v>
       </c>
-      <c r="F293" s="8"/>
-      <c r="G293" s="8"/>
+      <c r="F293" s="4"/>
+      <c r="G293" s="4"/>
     </row>
     <row r="294" ht="76.75" spans="1:7">
       <c r="A294" s="4" t="s">
@@ -10233,14 +10233,14 @@
       <c r="C294" s="4" t="s">
         <v>1152</v>
       </c>
-      <c r="D294" s="4" t="s">
+      <c r="D294" s="5" t="s">
         <v>1153</v>
       </c>
-      <c r="E294" s="7">
+      <c r="E294" s="8">
         <v>0</v>
       </c>
-      <c r="F294" s="8"/>
-      <c r="G294" s="8"/>
+      <c r="F294" s="4"/>
+      <c r="G294" s="4"/>
     </row>
     <row r="295" ht="244.75" spans="1:7">
       <c r="A295" s="4" t="s">
@@ -10252,14 +10252,14 @@
       <c r="C295" s="4" t="s">
         <v>1156</v>
       </c>
-      <c r="D295" s="4" t="s">
+      <c r="D295" s="5" t="s">
         <v>1157</v>
       </c>
-      <c r="E295" s="7">
+      <c r="E295" s="8">
         <v>0</v>
       </c>
-      <c r="F295" s="8"/>
-      <c r="G295" s="8"/>
+      <c r="F295" s="4"/>
+      <c r="G295" s="4"/>
     </row>
     <row r="296" ht="274.75" spans="1:7">
       <c r="A296" s="4" t="s">
@@ -10271,14 +10271,14 @@
       <c r="C296" s="4" t="s">
         <v>1159</v>
       </c>
-      <c r="D296" s="4" t="s">
+      <c r="D296" s="5" t="s">
         <v>1160</v>
       </c>
-      <c r="E296" s="7">
+      <c r="E296" s="8">
         <v>0</v>
       </c>
-      <c r="F296" s="8"/>
-      <c r="G296" s="8"/>
+      <c r="F296" s="4"/>
+      <c r="G296" s="4"/>
     </row>
     <row r="297" ht="244.75" spans="1:7">
       <c r="A297" s="4" t="s">
@@ -10290,14 +10290,14 @@
       <c r="C297" s="4" t="s">
         <v>1163</v>
       </c>
-      <c r="D297" s="4" t="s">
+      <c r="D297" s="5" t="s">
         <v>1164</v>
       </c>
-      <c r="E297" s="7">
+      <c r="E297" s="8">
         <v>0</v>
       </c>
-      <c r="F297" s="8"/>
-      <c r="G297" s="8"/>
+      <c r="F297" s="4"/>
+      <c r="G297" s="4"/>
     </row>
     <row r="298" ht="213.75" spans="1:7">
       <c r="A298" s="4" t="s">
@@ -10309,14 +10309,14 @@
       <c r="C298" s="4" t="s">
         <v>1167</v>
       </c>
-      <c r="D298" s="4" t="s">
+      <c r="D298" s="5" t="s">
         <v>1168</v>
       </c>
-      <c r="E298" s="7">
+      <c r="E298" s="8">
         <v>0</v>
       </c>
-      <c r="F298" s="8"/>
-      <c r="G298" s="8"/>
+      <c r="F298" s="4"/>
+      <c r="G298" s="4"/>
     </row>
     <row r="299" ht="244.75" spans="1:7">
       <c r="A299" s="4" t="s">
@@ -10328,14 +10328,14 @@
       <c r="C299" s="4" t="s">
         <v>1171</v>
       </c>
-      <c r="D299" s="4" t="s">
+      <c r="D299" s="5" t="s">
         <v>1172</v>
       </c>
-      <c r="E299" s="7">
+      <c r="E299" s="8">
         <v>0</v>
       </c>
-      <c r="F299" s="8"/>
-      <c r="G299" s="8"/>
+      <c r="F299" s="4"/>
+      <c r="G299" s="4"/>
     </row>
     <row r="300" ht="213.75" spans="1:7">
       <c r="A300" s="4" t="s">
@@ -10347,14 +10347,14 @@
       <c r="C300" s="4" t="s">
         <v>1175</v>
       </c>
-      <c r="D300" s="4" t="s">
+      <c r="D300" s="5" t="s">
         <v>1176</v>
       </c>
-      <c r="E300" s="7">
+      <c r="E300" s="8">
         <v>0</v>
       </c>
-      <c r="F300" s="8"/>
-      <c r="G300" s="8"/>
+      <c r="F300" s="4"/>
+      <c r="G300" s="4"/>
     </row>
     <row r="301" ht="259.75" spans="1:7">
       <c r="A301" s="4" t="s">
@@ -10366,14 +10366,14 @@
       <c r="C301" s="4" t="s">
         <v>1179</v>
       </c>
-      <c r="D301" s="4" t="s">
+      <c r="D301" s="5" t="s">
         <v>1180</v>
       </c>
-      <c r="E301" s="7">
+      <c r="E301" s="8">
         <v>0</v>
       </c>
-      <c r="F301" s="8"/>
-      <c r="G301" s="8"/>
+      <c r="F301" s="4"/>
+      <c r="G301" s="4"/>
     </row>
     <row r="302" ht="244.75" spans="1:7">
       <c r="A302" s="4" t="s">
@@ -10385,14 +10385,14 @@
       <c r="C302" s="4" t="s">
         <v>1183</v>
       </c>
-      <c r="D302" s="4" t="s">
+      <c r="D302" s="5" t="s">
         <v>1184</v>
       </c>
-      <c r="E302" s="7">
+      <c r="E302" s="8">
         <v>0</v>
       </c>
-      <c r="F302" s="8"/>
-      <c r="G302" s="8"/>
+      <c r="F302" s="4"/>
+      <c r="G302" s="4"/>
     </row>
     <row r="303" ht="274.75" spans="1:7">
       <c r="A303" s="4" t="s">
@@ -10404,14 +10404,14 @@
       <c r="C303" s="4" t="s">
         <v>1187</v>
       </c>
-      <c r="D303" s="4" t="s">
+      <c r="D303" s="5" t="s">
         <v>1188</v>
       </c>
-      <c r="E303" s="7">
+      <c r="E303" s="8">
         <v>0</v>
       </c>
-      <c r="F303" s="8"/>
-      <c r="G303" s="8"/>
+      <c r="F303" s="4"/>
+      <c r="G303" s="4"/>
     </row>
     <row r="304" ht="335.75" spans="1:7">
       <c r="A304" s="4" t="s">
@@ -10423,14 +10423,14 @@
       <c r="C304" s="4" t="s">
         <v>1191</v>
       </c>
-      <c r="D304" s="4" t="s">
+      <c r="D304" s="5" t="s">
         <v>1192</v>
       </c>
-      <c r="E304" s="7">
+      <c r="E304" s="8">
         <v>0</v>
       </c>
-      <c r="F304" s="8"/>
-      <c r="G304" s="8"/>
+      <c r="F304" s="4"/>
+      <c r="G304" s="4"/>
     </row>
     <row r="305" ht="122.75" spans="1:7">
       <c r="A305" s="4" t="s">
@@ -10442,14 +10442,14 @@
       <c r="C305" s="4" t="s">
         <v>1195</v>
       </c>
-      <c r="D305" s="4" t="s">
+      <c r="D305" s="5" t="s">
         <v>1196</v>
       </c>
-      <c r="E305" s="7">
+      <c r="E305" s="8">
         <v>0</v>
       </c>
-      <c r="F305" s="8"/>
-      <c r="G305" s="8"/>
+      <c r="F305" s="4"/>
+      <c r="G305" s="4"/>
     </row>
     <row r="306" ht="274.75" spans="1:5">
       <c r="A306" s="4" t="s">
@@ -10461,10 +10461,10 @@
       <c r="C306" s="4" t="s">
         <v>1199</v>
       </c>
-      <c r="D306" s="4" t="s">
+      <c r="D306" s="5" t="s">
         <v>1200</v>
       </c>
-      <c r="E306" s="7">
+      <c r="E306" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10478,10 +10478,10 @@
       <c r="C307" s="4" t="s">
         <v>1203</v>
       </c>
-      <c r="D307" s="4" t="s">
+      <c r="D307" s="5" t="s">
         <v>1204</v>
       </c>
-      <c r="E307" s="7">
+      <c r="E307" s="8">
         <v>0</v>
       </c>
     </row>
@@ -10495,10 +10495,10 @@
       <c r="C308" s="4" t="s">
         <v>1207</v>
       </c>
-      <c r="D308" s="4" t="s">
+      <c r="D308" s="5" t="s">
         <v>1208</v>
       </c>
-      <c r="E308" s="7">
+      <c r="E308" s="8">
         <v>0</v>
       </c>
     </row>
